--- a/data/phoneme_onset_D/St10_D.xlsx
+++ b/data/phoneme_onset_D/St10_D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/IMT/TESI/linguistic_pipeline_EEG/data/phoneme_onset_D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_79A572AAD310D760335A2F11595ED87656DF7603" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B73AA9A-305F-4CF2-A22F-9871CA2994BD}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="6_{D6F9A13C-254F-4EFF-BB37-6ACBF87AA487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB392BCC-5E29-4746-BC9E-28BDDC153C07}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7155" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7158" uniqueCount="664">
   <si>
     <t>BEGIN</t>
   </si>
@@ -2431,7 +2431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2384"/>
+  <dimension ref="A1:N2385"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" width="18.7265625" bestFit="1" customWidth="1"/>
@@ -3753,7 +3753,7 @@
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="F65" t="s">
         <v>57</v>
@@ -4721,7 +4721,7 @@
         <v>29</v>
       </c>
       <c r="D114" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="F114" t="s">
         <v>80</v>
@@ -4841,7 +4841,7 @@
         <v>29</v>
       </c>
       <c r="D120" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="F120" t="s">
         <v>80</v>
@@ -6457,7 +6457,7 @@
         <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F202" t="s">
         <v>109</v>
@@ -6577,7 +6577,7 @@
         <v>54</v>
       </c>
       <c r="D208" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="F208" t="s">
         <v>80</v>
@@ -6691,7 +6691,7 @@
         <v>54</v>
       </c>
       <c r="D214" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="F214" t="s">
         <v>80</v>
@@ -7205,7 +7205,7 @@
         <v>60</v>
       </c>
       <c r="D240" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F240" t="s">
         <v>23</v>
@@ -7384,7 +7384,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C250">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D250" t="s">
         <v>20</v>
@@ -7507,7 +7507,7 @@
         <v>66</v>
       </c>
       <c r="D256" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="F256" t="s">
         <v>127</v>
@@ -8367,7 +8367,7 @@
         <v>77</v>
       </c>
       <c r="D299" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F299" t="s">
         <v>147</v>
@@ -8467,7 +8467,7 @@
         <v>78</v>
       </c>
       <c r="D304" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F304" t="s">
         <v>149</v>
@@ -8478,7 +8478,7 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C305">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D305" t="s">
         <v>30</v>
@@ -8601,7 +8601,7 @@
         <v>81</v>
       </c>
       <c r="D311" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="F311" t="s">
         <v>127</v>
@@ -12491,7 +12491,7 @@
         <v>129</v>
       </c>
       <c r="D507" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F507" t="s">
         <v>200</v>
@@ -12851,7 +12851,7 @@
         <v>132</v>
       </c>
       <c r="D525" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F525" t="s">
         <v>206</v>
@@ -13536,7 +13536,7 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C560">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D560" t="s">
         <v>50</v>
@@ -14239,7 +14239,7 @@
         <v>147</v>
       </c>
       <c r="D595" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="F595" t="s">
         <v>227</v>
@@ -14650,7 +14650,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C616">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D616" t="s">
         <v>73</v>
@@ -17802,7 +17802,7 @@
         <v>184</v>
       </c>
       <c r="D776" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F776" t="s">
         <v>275</v>
@@ -18507,7 +18507,7 @@
         <v>193</v>
       </c>
       <c r="D812" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F812" t="s">
         <v>285</v>
@@ -27289,7 +27289,7 @@
         <v>290</v>
       </c>
       <c r="D1255" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="F1255" t="s">
         <v>396</v>
@@ -27809,7 +27809,7 @@
         <v>295</v>
       </c>
       <c r="D1281" t="s">
-        <v>659</v>
+        <v>19</v>
       </c>
       <c r="F1281" t="s">
         <v>402</v>
@@ -28503,7 +28503,7 @@
         <v>302</v>
       </c>
       <c r="D1316" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F1316" t="s">
         <v>43</v>
@@ -30391,7 +30391,7 @@
         <v>324</v>
       </c>
       <c r="D1411" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="F1411" t="s">
         <v>231</v>
@@ -30431,7 +30431,7 @@
         <v>324</v>
       </c>
       <c r="D1413" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="F1413" t="s">
         <v>231</v>
@@ -30471,7 +30471,7 @@
         <v>325</v>
       </c>
       <c r="D1415" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="F1415" t="s">
         <v>90</v>
@@ -30611,7 +30611,7 @@
         <v>327</v>
       </c>
       <c r="D1422" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F1422" t="s">
         <v>432</v>
@@ -30811,7 +30811,7 @@
         <v>329</v>
       </c>
       <c r="D1432" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F1432" t="s">
         <v>434</v>
@@ -31071,7 +31071,7 @@
         <v>331</v>
       </c>
       <c r="D1445" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="F1445" t="s">
         <v>436</v>
@@ -32431,7 +32431,7 @@
         <v>347</v>
       </c>
       <c r="D1513" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="F1513" t="s">
         <v>459</v>
@@ -34567,7 +34567,7 @@
         <v>373</v>
       </c>
       <c r="D1621" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="F1621" t="s">
         <v>485</v>
@@ -35147,7 +35147,7 @@
         <v>380</v>
       </c>
       <c r="D1650" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F1650" t="s">
         <v>492</v>
@@ -35441,7 +35441,7 @@
         <v>384</v>
       </c>
       <c r="D1665" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F1665" t="s">
         <v>495</v>
@@ -35541,7 +35541,7 @@
         <v>384</v>
       </c>
       <c r="D1670" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="F1670" t="s">
         <v>495</v>
@@ -40741,7 +40741,7 @@
         <v>439</v>
       </c>
       <c r="D1933" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F1933" t="s">
         <v>559</v>
@@ -43339,37 +43339,31 @@
       </c>
     </row>
     <row r="2064" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2064">
-        <v>7758513</v>
-      </c>
-      <c r="B2064">
-        <v>1763</v>
-      </c>
       <c r="C2064">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D2064" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="F2064" t="s">
-        <v>140</v>
+        <v>585</v>
       </c>
       <c r="G2064" t="s">
-        <v>141</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2065" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2065">
-        <v>7760277</v>
+        <v>7758513</v>
       </c>
       <c r="B2065">
-        <v>4850</v>
+        <v>1763</v>
       </c>
       <c r="C2065">
         <v>468</v>
       </c>
       <c r="D2065" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="F2065" t="s">
         <v>140</v>
@@ -43380,36 +43374,36 @@
     </row>
     <row r="2066" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2066">
-        <v>7765128</v>
+        <v>7760277</v>
       </c>
       <c r="B2066">
-        <v>1322</v>
+        <v>4850</v>
       </c>
       <c r="C2066">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D2066" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2066" t="s">
-        <v>587</v>
+        <v>140</v>
       </c>
       <c r="G2066" t="s">
-        <v>588</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2067" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2067">
-        <v>7766451</v>
+        <v>7765128</v>
       </c>
       <c r="B2067">
-        <v>7055</v>
+        <v>1322</v>
       </c>
       <c r="C2067">
         <v>469</v>
       </c>
       <c r="D2067" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F2067" t="s">
         <v>587</v>
@@ -43420,16 +43414,16 @@
     </row>
     <row r="2068" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2068">
-        <v>7773507</v>
+        <v>7766451</v>
       </c>
       <c r="B2068">
-        <v>1322</v>
+        <v>7055</v>
       </c>
       <c r="C2068">
         <v>469</v>
       </c>
       <c r="D2068" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F2068" t="s">
         <v>587</v>
@@ -43440,16 +43434,16 @@
     </row>
     <row r="2069" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2069">
-        <v>7774830</v>
+        <v>7773507</v>
       </c>
       <c r="B2069">
-        <v>5732</v>
+        <v>1322</v>
       </c>
       <c r="C2069">
         <v>469</v>
       </c>
       <c r="D2069" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F2069" t="s">
         <v>587</v>
@@ -43460,16 +43454,16 @@
     </row>
     <row r="2070" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2070">
-        <v>7780563</v>
+        <v>7774830</v>
       </c>
       <c r="B2070">
-        <v>1322</v>
+        <v>5732</v>
       </c>
       <c r="C2070">
         <v>469</v>
       </c>
       <c r="D2070" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F2070" t="s">
         <v>587</v>
@@ -43480,16 +43474,16 @@
     </row>
     <row r="2071" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2071">
-        <v>7781886</v>
+        <v>7780563</v>
       </c>
       <c r="B2071">
-        <v>2645</v>
+        <v>1322</v>
       </c>
       <c r="C2071">
         <v>469</v>
       </c>
       <c r="D2071" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F2071" t="s">
         <v>587</v>
@@ -43500,16 +43494,16 @@
     </row>
     <row r="2072" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2072">
-        <v>7784532</v>
+        <v>7781886</v>
       </c>
       <c r="B2072">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2072">
         <v>469</v>
       </c>
       <c r="D2072" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2072" t="s">
         <v>587</v>
@@ -43520,16 +43514,16 @@
     </row>
     <row r="2073" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2073">
-        <v>7786737</v>
+        <v>7784532</v>
       </c>
       <c r="B2073">
-        <v>5732</v>
+        <v>2204</v>
       </c>
       <c r="C2073">
         <v>469</v>
       </c>
       <c r="D2073" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2073" t="s">
         <v>587</v>
@@ -43540,36 +43534,36 @@
     </row>
     <row r="2074" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2074">
-        <v>7796880</v>
+        <v>7786737</v>
       </c>
       <c r="B2074">
-        <v>3086</v>
+        <v>5732</v>
       </c>
       <c r="C2074">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D2074" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2074" t="s">
-        <v>121</v>
+        <v>587</v>
       </c>
       <c r="G2074" t="s">
-        <v>122</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2075" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2075">
-        <v>7799967</v>
+        <v>7796880</v>
       </c>
       <c r="B2075">
-        <v>2645</v>
+        <v>3086</v>
       </c>
       <c r="C2075">
         <v>470</v>
       </c>
       <c r="D2075" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2075" t="s">
         <v>121</v>
@@ -43580,36 +43574,36 @@
     </row>
     <row r="2076" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2076">
-        <v>7802613</v>
+        <v>7799967</v>
       </c>
       <c r="B2076">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2076">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D2076" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F2076" t="s">
-        <v>589</v>
+        <v>121</v>
       </c>
       <c r="G2076" t="s">
-        <v>590</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2077" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2077">
-        <v>7806141</v>
+        <v>7802613</v>
       </c>
       <c r="B2077">
-        <v>1763</v>
+        <v>3527</v>
       </c>
       <c r="C2077">
         <v>471</v>
       </c>
       <c r="D2077" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F2077" t="s">
         <v>589</v>
@@ -43620,16 +43614,16 @@
     </row>
     <row r="2078" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2078">
-        <v>7807905</v>
+        <v>7806141</v>
       </c>
       <c r="B2078">
-        <v>2204</v>
+        <v>1763</v>
       </c>
       <c r="C2078">
         <v>471</v>
       </c>
       <c r="D2078" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2078" t="s">
         <v>589</v>
@@ -43640,16 +43634,16 @@
     </row>
     <row r="2079" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2079">
-        <v>7810110</v>
+        <v>7807905</v>
       </c>
       <c r="B2079">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2079">
         <v>471</v>
       </c>
       <c r="D2079" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F2079" t="s">
         <v>589</v>
@@ -43660,36 +43654,36 @@
     </row>
     <row r="2080" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2080">
-        <v>7811874</v>
+        <v>7810110</v>
       </c>
       <c r="B2080">
-        <v>3086</v>
+        <v>1763</v>
       </c>
       <c r="C2080">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D2080" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F2080" t="s">
-        <v>322</v>
+        <v>589</v>
       </c>
       <c r="G2080" t="s">
-        <v>323</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2081" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2081">
-        <v>7814961</v>
+        <v>7811874</v>
       </c>
       <c r="B2081">
-        <v>5291</v>
+        <v>3086</v>
       </c>
       <c r="C2081">
         <v>472</v>
       </c>
       <c r="D2081" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F2081" t="s">
         <v>322</v>
@@ -43700,36 +43694,36 @@
     </row>
     <row r="2082" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2082">
-        <v>7820253</v>
+        <v>7814961</v>
       </c>
       <c r="B2082">
-        <v>1322</v>
+        <v>5291</v>
       </c>
       <c r="C2082">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D2082" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2082" t="s">
-        <v>194</v>
+        <v>322</v>
       </c>
       <c r="G2082" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2083" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2083">
-        <v>7821576</v>
+        <v>7820253</v>
       </c>
       <c r="B2083">
-        <v>2204</v>
+        <v>1322</v>
       </c>
       <c r="C2083">
         <v>473</v>
       </c>
       <c r="D2083" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F2083" t="s">
         <v>194</v>
@@ -43740,36 +43734,36 @@
     </row>
     <row r="2084" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2084">
-        <v>7823781</v>
+        <v>7821576</v>
       </c>
       <c r="B2084">
-        <v>3086</v>
+        <v>2204</v>
       </c>
       <c r="C2084">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D2084" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2084" t="s">
-        <v>591</v>
+        <v>194</v>
       </c>
       <c r="G2084" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2085" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2085">
-        <v>7826868</v>
+        <v>7823781</v>
       </c>
       <c r="B2085">
-        <v>1322</v>
+        <v>3086</v>
       </c>
       <c r="C2085">
         <v>474</v>
       </c>
       <c r="D2085" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F2085" t="s">
         <v>591</v>
@@ -43780,16 +43774,16 @@
     </row>
     <row r="2086" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2086">
-        <v>7828191</v>
+        <v>7826868</v>
       </c>
       <c r="B2086">
-        <v>6614</v>
+        <v>1322</v>
       </c>
       <c r="C2086">
         <v>474</v>
       </c>
       <c r="D2086" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F2086" t="s">
         <v>591</v>
@@ -43800,36 +43794,36 @@
     </row>
     <row r="2087" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2087">
-        <v>7834806</v>
+        <v>7828191</v>
       </c>
       <c r="B2087">
-        <v>1322</v>
+        <v>6614</v>
       </c>
       <c r="C2087">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D2087" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2087" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G2087" t="s">
-        <v>593</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2088" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2088">
-        <v>7836129</v>
+        <v>7834806</v>
       </c>
       <c r="B2088">
-        <v>3086</v>
+        <v>1322</v>
       </c>
       <c r="C2088">
         <v>475</v>
       </c>
       <c r="D2088" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2088" t="s">
         <v>592</v>
@@ -43840,16 +43834,16 @@
     </row>
     <row r="2089" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2089">
-        <v>7839216</v>
+        <v>7836129</v>
       </c>
       <c r="B2089">
-        <v>2204</v>
+        <v>3086</v>
       </c>
       <c r="C2089">
         <v>475</v>
       </c>
       <c r="D2089" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F2089" t="s">
         <v>592</v>
@@ -43860,7 +43854,7 @@
     </row>
     <row r="2090" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2090">
-        <v>7841421</v>
+        <v>7839216</v>
       </c>
       <c r="B2090">
         <v>2204</v>
@@ -43869,7 +43863,7 @@
         <v>475</v>
       </c>
       <c r="D2090" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2090" t="s">
         <v>592</v>
@@ -43880,7 +43874,7 @@
     </row>
     <row r="2091" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2091">
-        <v>7843626</v>
+        <v>7841421</v>
       </c>
       <c r="B2091">
         <v>2204</v>
@@ -43889,7 +43883,7 @@
         <v>475</v>
       </c>
       <c r="D2091" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F2091" t="s">
         <v>592</v>
@@ -43900,16 +43894,16 @@
     </row>
     <row r="2092" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2092">
-        <v>7845831</v>
+        <v>7843626</v>
       </c>
       <c r="B2092">
-        <v>8378</v>
+        <v>2204</v>
       </c>
       <c r="C2092">
         <v>475</v>
       </c>
       <c r="D2092" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2092" t="s">
         <v>592</v>
@@ -43920,16 +43914,16 @@
     </row>
     <row r="2093" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2093">
-        <v>7854210</v>
+        <v>7845831</v>
       </c>
       <c r="B2093">
-        <v>1763</v>
+        <v>8378</v>
       </c>
       <c r="C2093">
         <v>475</v>
       </c>
       <c r="D2093" t="s">
-        <v>594</v>
+        <v>21</v>
       </c>
       <c r="F2093" t="s">
         <v>592</v>
@@ -43940,16 +43934,16 @@
     </row>
     <row r="2094" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2094">
-        <v>7855974</v>
+        <v>7854210</v>
       </c>
       <c r="B2094">
-        <v>7496</v>
+        <v>1763</v>
       </c>
       <c r="C2094">
         <v>475</v>
       </c>
       <c r="D2094" t="s">
-        <v>14</v>
+        <v>594</v>
       </c>
       <c r="F2094" t="s">
         <v>592</v>
@@ -43960,16 +43954,16 @@
     </row>
     <row r="2095" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2095">
-        <v>7863471</v>
+        <v>7855974</v>
       </c>
       <c r="B2095">
-        <v>3968</v>
+        <v>7496</v>
       </c>
       <c r="C2095">
         <v>475</v>
       </c>
       <c r="D2095" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2095" t="s">
         <v>592</v>
@@ -43980,16 +43974,16 @@
     </row>
     <row r="2096" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2096">
-        <v>7867440</v>
+        <v>7863471</v>
       </c>
       <c r="B2096">
-        <v>1322</v>
+        <v>3968</v>
       </c>
       <c r="C2096">
         <v>475</v>
       </c>
       <c r="D2096" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F2096" t="s">
         <v>592</v>
@@ -44000,16 +43994,16 @@
     </row>
     <row r="2097" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2097">
-        <v>7868763</v>
+        <v>7867440</v>
       </c>
       <c r="B2097">
-        <v>1763</v>
+        <v>1322</v>
       </c>
       <c r="C2097">
         <v>475</v>
       </c>
       <c r="D2097" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="F2097" t="s">
         <v>592</v>
@@ -44020,56 +44014,56 @@
     </row>
     <row r="2098" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2098">
-        <v>7870527</v>
+        <v>7868763</v>
       </c>
       <c r="B2098">
-        <v>1322</v>
+        <v>1763</v>
       </c>
       <c r="C2098">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D2098" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F2098" t="s">
-        <v>23</v>
+        <v>592</v>
       </c>
       <c r="G2098" t="s">
-        <v>51</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2099" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2099">
-        <v>7871850</v>
+        <v>7870527</v>
       </c>
       <c r="B2099">
-        <v>1763</v>
+        <v>1322</v>
       </c>
       <c r="C2099">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D2099" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="F2099" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
       <c r="G2099" t="s">
-        <v>210</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2100">
-        <v>7873614</v>
+        <v>7871850</v>
       </c>
       <c r="B2100">
-        <v>3527</v>
+        <v>1763</v>
       </c>
       <c r="C2100">
         <v>477</v>
       </c>
       <c r="D2100" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="F2100" t="s">
         <v>209</v>
@@ -44080,36 +44074,36 @@
     </row>
     <row r="2101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2101">
-        <v>7877142</v>
+        <v>7873614</v>
       </c>
       <c r="B2101">
-        <v>4850</v>
+        <v>3527</v>
       </c>
       <c r="C2101">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D2101" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="F2101" t="s">
-        <v>595</v>
+        <v>209</v>
       </c>
       <c r="G2101" t="s">
-        <v>596</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2102">
-        <v>7881993</v>
+        <v>7877142</v>
       </c>
       <c r="B2102">
-        <v>3968</v>
+        <v>4850</v>
       </c>
       <c r="C2102">
         <v>478</v>
       </c>
       <c r="D2102" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="F2102" t="s">
         <v>595</v>
@@ -44120,16 +44114,16 @@
     </row>
     <row r="2103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2103">
-        <v>7885962</v>
+        <v>7881993</v>
       </c>
       <c r="B2103">
-        <v>1763</v>
+        <v>3968</v>
       </c>
       <c r="C2103">
         <v>478</v>
       </c>
       <c r="D2103" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="F2103" t="s">
         <v>595</v>
@@ -44140,36 +44134,36 @@
     </row>
     <row r="2104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2104">
-        <v>7887726</v>
+        <v>7885962</v>
       </c>
       <c r="B2104">
-        <v>2204</v>
+        <v>1763</v>
       </c>
       <c r="C2104">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D2104" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="F2104" t="s">
-        <v>322</v>
+        <v>595</v>
       </c>
       <c r="G2104" t="s">
-        <v>323</v>
+        <v>596</v>
       </c>
     </row>
     <row r="2105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2105">
-        <v>7889931</v>
+        <v>7887726</v>
       </c>
       <c r="B2105">
-        <v>6173</v>
+        <v>2204</v>
       </c>
       <c r="C2105">
         <v>479</v>
       </c>
       <c r="D2105" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F2105" t="s">
         <v>322</v>
@@ -44180,36 +44174,36 @@
     </row>
     <row r="2106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2106">
-        <v>7896105</v>
+        <v>7889931</v>
       </c>
       <c r="B2106">
-        <v>1322</v>
+        <v>6173</v>
       </c>
       <c r="C2106">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D2106" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2106" t="s">
-        <v>194</v>
+        <v>322</v>
       </c>
       <c r="G2106" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2107">
-        <v>7897428</v>
+        <v>7896105</v>
       </c>
       <c r="B2107">
-        <v>2204</v>
+        <v>1322</v>
       </c>
       <c r="C2107">
         <v>480</v>
       </c>
       <c r="D2107" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F2107" t="s">
         <v>194</v>
@@ -44220,36 +44214,36 @@
     </row>
     <row r="2108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2108">
-        <v>7899633</v>
+        <v>7897428</v>
       </c>
       <c r="B2108">
-        <v>1322</v>
+        <v>2204</v>
       </c>
       <c r="C2108">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D2108" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F2108" t="s">
-        <v>597</v>
+        <v>194</v>
       </c>
       <c r="G2108" t="s">
-        <v>598</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2109">
-        <v>7900956</v>
+        <v>7899633</v>
       </c>
       <c r="B2109">
-        <v>6614</v>
+        <v>1322</v>
       </c>
       <c r="C2109">
         <v>481</v>
       </c>
       <c r="D2109" t="s">
-        <v>270</v>
+        <v>14</v>
       </c>
       <c r="F2109" t="s">
         <v>597</v>
@@ -44260,16 +44254,16 @@
     </row>
     <row r="2110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2110">
-        <v>7907571</v>
+        <v>7900956</v>
       </c>
       <c r="B2110">
-        <v>9701</v>
+        <v>6614</v>
       </c>
       <c r="C2110">
         <v>481</v>
       </c>
       <c r="D2110" t="s">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="F2110" t="s">
         <v>597</v>
@@ -44280,16 +44274,16 @@
     </row>
     <row r="2111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2111">
-        <v>7917273</v>
+        <v>7907571</v>
       </c>
       <c r="B2111">
-        <v>6173</v>
+        <v>9701</v>
       </c>
       <c r="C2111">
         <v>481</v>
       </c>
       <c r="D2111" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F2111" t="s">
         <v>597</v>
@@ -44300,16 +44294,16 @@
     </row>
     <row r="2112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2112">
-        <v>7923447</v>
+        <v>7917273</v>
       </c>
       <c r="B2112">
-        <v>2204</v>
+        <v>6173</v>
       </c>
       <c r="C2112">
         <v>481</v>
       </c>
       <c r="D2112" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F2112" t="s">
         <v>597</v>
@@ -44320,16 +44314,16 @@
     </row>
     <row r="2113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2113">
-        <v>7925652</v>
+        <v>7923447</v>
       </c>
       <c r="B2113">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2113">
         <v>481</v>
       </c>
       <c r="D2113" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2113" t="s">
         <v>597</v>
@@ -44340,16 +44334,16 @@
     </row>
     <row r="2114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2114">
-        <v>7928298</v>
+        <v>7925652</v>
       </c>
       <c r="B2114">
-        <v>5732</v>
+        <v>2645</v>
       </c>
       <c r="C2114">
         <v>481</v>
       </c>
       <c r="D2114" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F2114" t="s">
         <v>597</v>
@@ -44360,36 +44354,36 @@
     </row>
     <row r="2115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2115">
-        <v>7964019</v>
+        <v>7928298</v>
       </c>
       <c r="B2115">
-        <v>3086</v>
+        <v>5732</v>
       </c>
       <c r="C2115">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D2115" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F2115" t="s">
-        <v>287</v>
+        <v>597</v>
       </c>
       <c r="G2115" t="s">
-        <v>141</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2116">
-        <v>7967106</v>
+        <v>7964019</v>
       </c>
       <c r="B2116">
-        <v>3527</v>
+        <v>3086</v>
       </c>
       <c r="C2116">
         <v>482</v>
       </c>
       <c r="D2116" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="F2116" t="s">
         <v>287</v>
@@ -44400,36 +44394,36 @@
     </row>
     <row r="2117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2117">
-        <v>7970634</v>
+        <v>7967106</v>
       </c>
       <c r="B2117">
-        <v>1763</v>
+        <v>3527</v>
       </c>
       <c r="C2117">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D2117" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2117" t="s">
-        <v>599</v>
+        <v>287</v>
       </c>
       <c r="G2117" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2118">
-        <v>7972398</v>
+        <v>7970634</v>
       </c>
       <c r="B2118">
-        <v>5291</v>
+        <v>1763</v>
       </c>
       <c r="C2118">
         <v>483</v>
       </c>
       <c r="D2118" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2118" t="s">
         <v>599</v>
@@ -44440,36 +44434,36 @@
     </row>
     <row r="2119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2119">
-        <v>7977690</v>
+        <v>7972398</v>
       </c>
       <c r="B2119">
         <v>5291</v>
       </c>
       <c r="C2119">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D2119" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2119" t="s">
-        <v>457</v>
+        <v>599</v>
       </c>
       <c r="G2119" t="s">
-        <v>458</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2120">
-        <v>7982982</v>
+        <v>7977690</v>
       </c>
       <c r="B2120">
-        <v>1322</v>
+        <v>5291</v>
       </c>
       <c r="C2120">
         <v>484</v>
       </c>
       <c r="D2120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2120" t="s">
         <v>457</v>
@@ -44480,36 +44474,36 @@
     </row>
     <row r="2121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2121">
-        <v>7984305</v>
+        <v>7982982</v>
       </c>
       <c r="B2121">
-        <v>1763</v>
+        <v>1322</v>
       </c>
       <c r="C2121">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D2121" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2121" t="s">
-        <v>600</v>
+        <v>457</v>
       </c>
       <c r="G2121" t="s">
-        <v>601</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2122">
-        <v>7986069</v>
+        <v>7984305</v>
       </c>
       <c r="B2122">
-        <v>3968</v>
+        <v>1763</v>
       </c>
       <c r="C2122">
         <v>485</v>
       </c>
       <c r="D2122" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F2122" t="s">
         <v>600</v>
@@ -44520,16 +44514,16 @@
     </row>
     <row r="2123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2123">
-        <v>7990038</v>
+        <v>7986069</v>
       </c>
       <c r="B2123">
-        <v>4850</v>
+        <v>3968</v>
       </c>
       <c r="C2123">
         <v>485</v>
       </c>
       <c r="D2123" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="F2123" t="s">
         <v>600</v>
@@ -44540,16 +44534,16 @@
     </row>
     <row r="2124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2124">
-        <v>7994889</v>
+        <v>7990038</v>
       </c>
       <c r="B2124">
-        <v>1763</v>
+        <v>4850</v>
       </c>
       <c r="C2124">
         <v>485</v>
       </c>
       <c r="D2124" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="F2124" t="s">
         <v>600</v>
@@ -44560,16 +44554,16 @@
     </row>
     <row r="2125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2125">
-        <v>7996653</v>
+        <v>7994889</v>
       </c>
       <c r="B2125">
-        <v>2204</v>
+        <v>1763</v>
       </c>
       <c r="C2125">
         <v>485</v>
       </c>
       <c r="D2125" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2125" t="s">
         <v>600</v>
@@ -44580,16 +44574,16 @@
     </row>
     <row r="2126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2126">
-        <v>7998858</v>
+        <v>7996653</v>
       </c>
       <c r="B2126">
-        <v>3086</v>
+        <v>2204</v>
       </c>
       <c r="C2126">
         <v>485</v>
       </c>
       <c r="D2126" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2126" t="s">
         <v>600</v>
@@ -44600,27 +44594,27 @@
     </row>
     <row r="2127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2127">
-        <v>8001945</v>
+        <v>7998858</v>
       </c>
       <c r="B2127">
-        <v>5291</v>
+        <v>3086</v>
       </c>
       <c r="C2127">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D2127" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F2127" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G2127" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2128">
-        <v>8007237</v>
+        <v>8001945</v>
       </c>
       <c r="B2128">
         <v>5291</v>
@@ -44629,7 +44623,7 @@
         <v>486</v>
       </c>
       <c r="D2128" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F2128" t="s">
         <v>602</v>
@@ -44640,16 +44634,16 @@
     </row>
     <row r="2129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2129">
-        <v>8012529</v>
+        <v>8007237</v>
       </c>
       <c r="B2129">
-        <v>1322</v>
+        <v>5291</v>
       </c>
       <c r="C2129">
         <v>486</v>
       </c>
       <c r="D2129" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F2129" t="s">
         <v>602</v>
@@ -44660,16 +44654,16 @@
     </row>
     <row r="2130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2130">
-        <v>8013852</v>
+        <v>8012529</v>
       </c>
       <c r="B2130">
-        <v>3527</v>
+        <v>1322</v>
       </c>
       <c r="C2130">
         <v>486</v>
       </c>
       <c r="D2130" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F2130" t="s">
         <v>602</v>
@@ -44679,11 +44673,17 @@
       </c>
     </row>
     <row r="2131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2131">
+        <v>8013852</v>
+      </c>
+      <c r="B2131">
+        <v>3527</v>
+      </c>
       <c r="C2131">
         <v>486</v>
       </c>
       <c r="D2131" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2131" t="s">
         <v>602</v>
@@ -44693,37 +44693,31 @@
       </c>
     </row>
     <row r="2132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2132">
-        <v>8017380</v>
-      </c>
-      <c r="B2132">
-        <v>3086</v>
-      </c>
       <c r="C2132">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D2132" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F2132" t="s">
-        <v>92</v>
+        <v>602</v>
       </c>
       <c r="G2132" t="s">
-        <v>93</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2133">
-        <v>8020467</v>
+        <v>8017380</v>
       </c>
       <c r="B2133">
-        <v>4188</v>
+        <v>3086</v>
       </c>
       <c r="C2133">
         <v>487</v>
       </c>
       <c r="D2133" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F2133" t="s">
         <v>92</v>
@@ -44733,11 +44727,17 @@
       </c>
     </row>
     <row r="2134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2134">
+        <v>8020467</v>
+      </c>
+      <c r="B2134">
+        <v>4188</v>
+      </c>
       <c r="C2134">
         <v>487</v>
       </c>
       <c r="D2134" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F2134" t="s">
         <v>92</v>
@@ -44747,37 +44747,31 @@
       </c>
     </row>
     <row r="2135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2135">
-        <v>8024656</v>
-      </c>
-      <c r="B2135">
-        <v>2865</v>
-      </c>
       <c r="C2135">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D2135" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F2135" t="s">
-        <v>604</v>
+        <v>92</v>
       </c>
       <c r="G2135" t="s">
-        <v>605</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2136">
-        <v>8027522</v>
+        <v>8024656</v>
       </c>
       <c r="B2136">
-        <v>1764</v>
+        <v>2865</v>
       </c>
       <c r="C2136">
         <v>488</v>
       </c>
       <c r="D2136" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="F2136" t="s">
         <v>604</v>
@@ -44788,16 +44782,16 @@
     </row>
     <row r="2137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2137">
-        <v>8029287</v>
+        <v>8027522</v>
       </c>
       <c r="B2137">
-        <v>5291</v>
+        <v>1764</v>
       </c>
       <c r="C2137">
         <v>488</v>
       </c>
       <c r="D2137" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F2137" t="s">
         <v>604</v>
@@ -44808,16 +44802,16 @@
     </row>
     <row r="2138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2138">
-        <v>8034579</v>
+        <v>8029287</v>
       </c>
       <c r="B2138">
-        <v>2204</v>
+        <v>5291</v>
       </c>
       <c r="C2138">
         <v>488</v>
       </c>
       <c r="D2138" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="F2138" t="s">
         <v>604</v>
@@ -44828,7 +44822,7 @@
     </row>
     <row r="2139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2139">
-        <v>8036784</v>
+        <v>8034579</v>
       </c>
       <c r="B2139">
         <v>2204</v>
@@ -44837,7 +44831,7 @@
         <v>488</v>
       </c>
       <c r="D2139" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="F2139" t="s">
         <v>604</v>
@@ -44848,36 +44842,36 @@
     </row>
     <row r="2140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2140">
-        <v>8038989</v>
+        <v>8036784</v>
       </c>
       <c r="B2140">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2140">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D2140" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="F2140" t="s">
-        <v>140</v>
+        <v>604</v>
       </c>
       <c r="G2140" t="s">
-        <v>141</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2141">
-        <v>8040753</v>
+        <v>8038989</v>
       </c>
       <c r="B2141">
-        <v>4409</v>
+        <v>1763</v>
       </c>
       <c r="C2141">
         <v>489</v>
       </c>
       <c r="D2141" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="F2141" t="s">
         <v>140</v>
@@ -44888,36 +44882,36 @@
     </row>
     <row r="2142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2142">
-        <v>8045163</v>
+        <v>8040753</v>
       </c>
       <c r="B2142">
-        <v>1322</v>
+        <v>4409</v>
       </c>
       <c r="C2142">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D2142" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2142" t="s">
-        <v>408</v>
+        <v>140</v>
       </c>
       <c r="G2142" t="s">
-        <v>409</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2143">
-        <v>8046486</v>
+        <v>8045163</v>
       </c>
       <c r="B2143">
-        <v>3086</v>
+        <v>1322</v>
       </c>
       <c r="C2143">
         <v>490</v>
       </c>
       <c r="D2143" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F2143" t="s">
         <v>408</v>
@@ -44928,16 +44922,16 @@
     </row>
     <row r="2144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2144">
-        <v>8049573</v>
+        <v>8046486</v>
       </c>
       <c r="B2144">
-        <v>2645</v>
+        <v>3086</v>
       </c>
       <c r="C2144">
         <v>490</v>
       </c>
       <c r="D2144" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="F2144" t="s">
         <v>408</v>
@@ -44948,16 +44942,16 @@
     </row>
     <row r="2145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2145">
-        <v>8052219</v>
+        <v>8049573</v>
       </c>
       <c r="B2145">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2145">
         <v>490</v>
       </c>
       <c r="D2145" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2145" t="s">
         <v>408</v>
@@ -44968,16 +44962,16 @@
     </row>
     <row r="2146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2146">
-        <v>8055747</v>
+        <v>8052219</v>
       </c>
       <c r="B2146">
-        <v>2204</v>
+        <v>3527</v>
       </c>
       <c r="C2146">
         <v>490</v>
       </c>
       <c r="D2146" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F2146" t="s">
         <v>408</v>
@@ -44988,16 +44982,16 @@
     </row>
     <row r="2147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2147">
-        <v>8057952</v>
+        <v>8055747</v>
       </c>
       <c r="B2147">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2147">
         <v>490</v>
       </c>
       <c r="D2147" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="F2147" t="s">
         <v>408</v>
@@ -45008,16 +45002,16 @@
     </row>
     <row r="2148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2148">
-        <v>8059716</v>
+        <v>8057952</v>
       </c>
       <c r="B2148">
-        <v>1322</v>
+        <v>1763</v>
       </c>
       <c r="C2148">
         <v>490</v>
       </c>
       <c r="D2148" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2148" t="s">
         <v>408</v>
@@ -45028,16 +45022,16 @@
     </row>
     <row r="2149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2149">
-        <v>8061039</v>
+        <v>8059716</v>
       </c>
       <c r="B2149">
-        <v>2204</v>
+        <v>1322</v>
       </c>
       <c r="C2149">
         <v>490</v>
       </c>
       <c r="D2149" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2149" t="s">
         <v>408</v>
@@ -45048,36 +45042,36 @@
     </row>
     <row r="2150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2150">
-        <v>8063244</v>
+        <v>8061039</v>
       </c>
       <c r="B2150">
-        <v>1322</v>
+        <v>2204</v>
       </c>
       <c r="C2150">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D2150" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="F2150" t="s">
-        <v>74</v>
+        <v>408</v>
       </c>
       <c r="G2150" t="s">
-        <v>75</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2151">
-        <v>8064567</v>
+        <v>8063244</v>
       </c>
       <c r="B2151">
-        <v>3086</v>
+        <v>1322</v>
       </c>
       <c r="C2151">
         <v>491</v>
       </c>
       <c r="D2151" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="F2151" t="s">
         <v>74</v>
@@ -45087,31 +45081,31 @@
       </c>
     </row>
     <row r="2152" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2152">
+        <v>8064567</v>
+      </c>
+      <c r="B2152">
+        <v>3086</v>
+      </c>
       <c r="C2152">
         <v>491</v>
       </c>
       <c r="D2152" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F2152" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="G2152" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2153" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2153">
-        <v>8067654</v>
-      </c>
-      <c r="B2153">
-        <v>6614</v>
-      </c>
       <c r="C2153">
         <v>492</v>
       </c>
       <c r="D2153" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F2153" t="s">
         <v>105</v>
@@ -45122,36 +45116,36 @@
     </row>
     <row r="2154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2154">
-        <v>8074269</v>
+        <v>8067654</v>
       </c>
       <c r="B2154">
-        <v>4850</v>
+        <v>6614</v>
       </c>
       <c r="C2154">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D2154" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F2154" t="s">
-        <v>606</v>
+        <v>105</v>
       </c>
       <c r="G2154" t="s">
-        <v>607</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2155">
-        <v>8079120</v>
+        <v>8074269</v>
       </c>
       <c r="B2155">
-        <v>7055</v>
+        <v>4850</v>
       </c>
       <c r="C2155">
         <v>493</v>
       </c>
       <c r="D2155" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F2155" t="s">
         <v>606</v>
@@ -45162,16 +45156,16 @@
     </row>
     <row r="2156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2156">
-        <v>8086176</v>
+        <v>8079120</v>
       </c>
       <c r="B2156">
-        <v>4850</v>
+        <v>7055</v>
       </c>
       <c r="C2156">
         <v>493</v>
       </c>
       <c r="D2156" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F2156" t="s">
         <v>606</v>
@@ -45182,16 +45176,16 @@
     </row>
     <row r="2157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2157">
-        <v>8091027</v>
+        <v>8086176</v>
       </c>
       <c r="B2157">
-        <v>5732</v>
+        <v>4850</v>
       </c>
       <c r="C2157">
         <v>493</v>
       </c>
       <c r="D2157" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F2157" t="s">
         <v>606</v>
@@ -45202,36 +45196,36 @@
     </row>
     <row r="2158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2158">
-        <v>8134686</v>
+        <v>8091027</v>
       </c>
       <c r="B2158">
-        <v>6173</v>
+        <v>5732</v>
       </c>
       <c r="C2158">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D2158" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F2158" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G2158" t="s">
-        <v>183</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2159">
-        <v>8140860</v>
+        <v>8134686</v>
       </c>
       <c r="B2159">
-        <v>1322</v>
+        <v>6173</v>
       </c>
       <c r="C2159">
         <v>494</v>
       </c>
       <c r="D2159" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F2159" t="s">
         <v>608</v>
@@ -45242,16 +45236,16 @@
     </row>
     <row r="2160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2160">
-        <v>8142183</v>
+        <v>8140860</v>
       </c>
       <c r="B2160">
-        <v>3527</v>
+        <v>1322</v>
       </c>
       <c r="C2160">
         <v>494</v>
       </c>
       <c r="D2160" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F2160" t="s">
         <v>608</v>
@@ -45262,16 +45256,16 @@
     </row>
     <row r="2161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2161">
-        <v>8145711</v>
+        <v>8142183</v>
       </c>
       <c r="B2161">
-        <v>2204</v>
+        <v>3527</v>
       </c>
       <c r="C2161">
         <v>494</v>
       </c>
       <c r="D2161" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F2161" t="s">
         <v>608</v>
@@ -45282,16 +45276,16 @@
     </row>
     <row r="2162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2162">
-        <v>8147916</v>
+        <v>8145711</v>
       </c>
       <c r="B2162">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2162">
         <v>494</v>
       </c>
       <c r="D2162" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F2162" t="s">
         <v>608</v>
@@ -45302,36 +45296,36 @@
     </row>
     <row r="2163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2163">
-        <v>8149680</v>
+        <v>8147916</v>
       </c>
       <c r="B2163">
-        <v>2645</v>
+        <v>1763</v>
       </c>
       <c r="C2163">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D2163" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F2163" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G2163" t="s">
-        <v>610</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2164">
-        <v>8152326</v>
+        <v>8149680</v>
       </c>
       <c r="B2164">
-        <v>3968</v>
+        <v>2645</v>
       </c>
       <c r="C2164">
         <v>495</v>
       </c>
       <c r="D2164" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F2164" t="s">
         <v>609</v>
@@ -45342,7 +45336,7 @@
     </row>
     <row r="2165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2165">
-        <v>8156295</v>
+        <v>8152326</v>
       </c>
       <c r="B2165">
         <v>3968</v>
@@ -45351,7 +45345,7 @@
         <v>495</v>
       </c>
       <c r="D2165" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2165" t="s">
         <v>609</v>
@@ -45362,16 +45356,16 @@
     </row>
     <row r="2166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2166">
-        <v>8160264</v>
+        <v>8156295</v>
       </c>
       <c r="B2166">
-        <v>1322</v>
+        <v>3968</v>
       </c>
       <c r="C2166">
         <v>495</v>
       </c>
       <c r="D2166" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2166" t="s">
         <v>609</v>
@@ -45382,16 +45376,16 @@
     </row>
     <row r="2167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2167">
-        <v>8161587</v>
+        <v>8160264</v>
       </c>
       <c r="B2167">
-        <v>3086</v>
+        <v>1322</v>
       </c>
       <c r="C2167">
         <v>495</v>
       </c>
       <c r="D2167" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F2167" t="s">
         <v>609</v>
@@ -45402,104 +45396,104 @@
     </row>
     <row r="2168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2168">
+        <v>8161587</v>
+      </c>
+      <c r="B2168">
+        <v>3086</v>
+      </c>
+      <c r="C2168">
+        <v>495</v>
+      </c>
+      <c r="D2168" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2168" t="s">
+        <v>609</v>
+      </c>
+      <c r="G2168" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2169">
         <v>8164674</v>
       </c>
-      <c r="B2168">
+      <c r="B2169">
         <v>2645</v>
       </c>
-      <c r="C2168">
-        <v>496</v>
-      </c>
-      <c r="D2168" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2168" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2168" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C2169">
         <v>496</v>
       </c>
       <c r="D2169" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2169" t="s">
         <v>90</v>
       </c>
       <c r="G2169" t="s">
-        <v>653</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C2170">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D2170" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2170" t="s">
-        <v>654</v>
+        <v>90</v>
       </c>
       <c r="G2170" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2171" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2171">
-        <v>8167320</v>
-      </c>
-      <c r="B2171">
-        <v>8378</v>
-      </c>
       <c r="C2171">
         <v>497</v>
       </c>
       <c r="D2171" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2171" t="s">
-        <v>125</v>
+        <v>654</v>
       </c>
       <c r="G2171" t="s">
-        <v>126</v>
+        <v>663</v>
       </c>
     </row>
     <row r="2172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2172">
-        <v>8175699</v>
+        <v>8167320</v>
       </c>
       <c r="B2172">
-        <v>1322</v>
+        <v>8378</v>
       </c>
       <c r="C2172">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D2172" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="F2172" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="G2172" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2173">
-        <v>8177022</v>
+        <v>8175699</v>
       </c>
       <c r="B2173">
-        <v>3968</v>
+        <v>1322</v>
       </c>
       <c r="C2173">
         <v>498</v>
       </c>
       <c r="D2173" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="F2173" t="s">
         <v>74</v>
@@ -45510,36 +45504,36 @@
     </row>
     <row r="2174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2174">
-        <v>8180991</v>
+        <v>8177022</v>
       </c>
       <c r="B2174">
-        <v>2204</v>
+        <v>3968</v>
       </c>
       <c r="C2174">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D2174" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F2174" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G2174" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2175">
-        <v>8183196</v>
+        <v>8180991</v>
       </c>
       <c r="B2175">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2175">
         <v>499</v>
       </c>
       <c r="D2175" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F2175" t="s">
         <v>76</v>
@@ -45550,16 +45544,16 @@
     </row>
     <row r="2176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2176">
-        <v>8185842</v>
+        <v>8183196</v>
       </c>
       <c r="B2176">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2176">
         <v>499</v>
       </c>
       <c r="D2176" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2176" t="s">
         <v>76</v>
@@ -45570,36 +45564,36 @@
     </row>
     <row r="2177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2177">
-        <v>8188047</v>
+        <v>8185842</v>
       </c>
       <c r="B2177">
         <v>2204</v>
       </c>
       <c r="C2177">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D2177" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F2177" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G2177" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2178">
-        <v>8190252</v>
+        <v>8188047</v>
       </c>
       <c r="B2178">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2178">
         <v>500</v>
       </c>
       <c r="D2178" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F2178" t="s">
         <v>92</v>
@@ -45610,16 +45604,16 @@
     </row>
     <row r="2179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2179">
-        <v>8192898</v>
+        <v>8190252</v>
       </c>
       <c r="B2179">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2179">
         <v>500</v>
       </c>
       <c r="D2179" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F2179" t="s">
         <v>92</v>
@@ -45630,36 +45624,36 @@
     </row>
     <row r="2180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2180">
-        <v>8196426</v>
+        <v>8192898</v>
       </c>
       <c r="B2180">
-        <v>4850</v>
+        <v>3527</v>
       </c>
       <c r="C2180">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D2180" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F2180" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G2180" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2181">
-        <v>8201277</v>
+        <v>8196426</v>
       </c>
       <c r="B2181">
-        <v>2204</v>
+        <v>4850</v>
       </c>
       <c r="C2181">
         <v>501</v>
       </c>
       <c r="D2181" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F2181" t="s">
         <v>97</v>
@@ -45670,16 +45664,16 @@
     </row>
     <row r="2182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2182">
-        <v>8203482</v>
+        <v>8201277</v>
       </c>
       <c r="B2182">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2182">
         <v>501</v>
       </c>
       <c r="D2182" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F2182" t="s">
         <v>97</v>
@@ -45690,36 +45684,36 @@
     </row>
     <row r="2183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2183">
-        <v>8205246</v>
+        <v>8203482</v>
       </c>
       <c r="B2183">
-        <v>5291</v>
+        <v>1763</v>
       </c>
       <c r="C2183">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D2183" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F2183" t="s">
-        <v>309</v>
+        <v>97</v>
       </c>
       <c r="G2183" t="s">
-        <v>310</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2184">
-        <v>8210538</v>
+        <v>8205246</v>
       </c>
       <c r="B2184">
-        <v>3086</v>
+        <v>5291</v>
       </c>
       <c r="C2184">
         <v>502</v>
       </c>
       <c r="D2184" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2184" t="s">
         <v>309</v>
@@ -45730,16 +45724,16 @@
     </row>
     <row r="2185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2185">
-        <v>8213625</v>
+        <v>8210538</v>
       </c>
       <c r="B2185">
-        <v>5291</v>
+        <v>3086</v>
       </c>
       <c r="C2185">
         <v>502</v>
       </c>
       <c r="D2185" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F2185" t="s">
         <v>309</v>
@@ -45750,16 +45744,16 @@
     </row>
     <row r="2186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2186">
-        <v>8218917</v>
+        <v>8213625</v>
       </c>
       <c r="B2186">
-        <v>6173</v>
+        <v>5291</v>
       </c>
       <c r="C2186">
         <v>502</v>
       </c>
       <c r="D2186" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F2186" t="s">
         <v>309</v>
@@ -45770,36 +45764,36 @@
     </row>
     <row r="2187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2187">
-        <v>8254638</v>
+        <v>8218917</v>
       </c>
       <c r="B2187">
-        <v>4409</v>
+        <v>6173</v>
       </c>
       <c r="C2187">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D2187" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2187" t="s">
-        <v>611</v>
+        <v>309</v>
       </c>
       <c r="G2187" t="s">
-        <v>70</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2188">
-        <v>8259048</v>
+        <v>8254638</v>
       </c>
       <c r="B2188">
-        <v>2204</v>
+        <v>4409</v>
       </c>
       <c r="C2188">
         <v>503</v>
       </c>
       <c r="D2188" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F2188" t="s">
         <v>611</v>
@@ -45810,56 +45804,56 @@
     </row>
     <row r="2189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2189">
-        <v>8261253</v>
+        <v>8259048</v>
       </c>
       <c r="B2189">
-        <v>3086</v>
+        <v>2204</v>
       </c>
       <c r="C2189">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D2189" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F2189" t="s">
-        <v>14</v>
+        <v>611</v>
       </c>
       <c r="G2189" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2190">
-        <v>8264340</v>
+        <v>8261253</v>
       </c>
       <c r="B2190">
-        <v>2204</v>
+        <v>3086</v>
       </c>
       <c r="C2190">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D2190" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F2190" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="G2190" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2191">
-        <v>8266545</v>
+        <v>8264340</v>
       </c>
       <c r="B2191">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2191">
         <v>505</v>
       </c>
       <c r="D2191" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F2191" t="s">
         <v>76</v>
@@ -45870,16 +45864,16 @@
     </row>
     <row r="2192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2192">
-        <v>8269191</v>
+        <v>8266545</v>
       </c>
       <c r="B2192">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2192">
         <v>505</v>
       </c>
       <c r="D2192" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2192" t="s">
         <v>76</v>
@@ -45890,36 +45884,36 @@
     </row>
     <row r="2193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2193">
-        <v>8270955</v>
+        <v>8269191</v>
       </c>
       <c r="B2193">
-        <v>1322</v>
+        <v>1763</v>
       </c>
       <c r="C2193">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D2193" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F2193" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G2193" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2194">
-        <v>8272278</v>
+        <v>8270955</v>
       </c>
       <c r="B2194">
-        <v>2204</v>
+        <v>1322</v>
       </c>
       <c r="C2194">
         <v>506</v>
       </c>
       <c r="D2194" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F2194" t="s">
         <v>92</v>
@@ -45930,16 +45924,16 @@
     </row>
     <row r="2195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2195">
-        <v>8274483</v>
+        <v>8272278</v>
       </c>
       <c r="B2195">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2195">
         <v>506</v>
       </c>
       <c r="D2195" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F2195" t="s">
         <v>92</v>
@@ -45950,56 +45944,56 @@
     </row>
     <row r="2196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2196">
-        <v>8277129</v>
+        <v>8274483</v>
       </c>
       <c r="B2196">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2196">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D2196" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F2196" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G2196" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2197">
-        <v>8279334</v>
+        <v>8277129</v>
       </c>
       <c r="B2197">
-        <v>6614</v>
+        <v>2204</v>
       </c>
       <c r="C2197">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D2197" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F2197" t="s">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="G2197" t="s">
-        <v>225</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2198">
-        <v>8285949</v>
+        <v>8279334</v>
       </c>
       <c r="B2198">
-        <v>4850</v>
+        <v>6614</v>
       </c>
       <c r="C2198">
         <v>508</v>
       </c>
       <c r="D2198" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F2198" t="s">
         <v>224</v>
@@ -46010,16 +46004,16 @@
     </row>
     <row r="2199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2199">
-        <v>8290800</v>
+        <v>8285949</v>
       </c>
       <c r="B2199">
-        <v>4409</v>
+        <v>4850</v>
       </c>
       <c r="C2199">
         <v>508</v>
       </c>
       <c r="D2199" t="s">
-        <v>226</v>
+        <v>50</v>
       </c>
       <c r="F2199" t="s">
         <v>224</v>
@@ -46030,16 +46024,16 @@
     </row>
     <row r="2200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2200">
-        <v>8295210</v>
+        <v>8290800</v>
       </c>
       <c r="B2200">
-        <v>7055</v>
+        <v>4409</v>
       </c>
       <c r="C2200">
         <v>508</v>
       </c>
       <c r="D2200" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="F2200" t="s">
         <v>224</v>
@@ -46050,16 +46044,16 @@
     </row>
     <row r="2201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2201">
-        <v>8302266</v>
+        <v>8295210</v>
       </c>
       <c r="B2201">
-        <v>6173</v>
+        <v>7055</v>
       </c>
       <c r="C2201">
         <v>508</v>
       </c>
       <c r="D2201" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F2201" t="s">
         <v>224</v>
@@ -46070,16 +46064,16 @@
     </row>
     <row r="2202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2202">
-        <v>8308440</v>
+        <v>8302266</v>
       </c>
       <c r="B2202">
-        <v>2204</v>
+        <v>6173</v>
       </c>
       <c r="C2202">
         <v>508</v>
       </c>
       <c r="D2202" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2202" t="s">
         <v>224</v>
@@ -46090,36 +46084,36 @@
     </row>
     <row r="2203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2203">
-        <v>8310645</v>
+        <v>8308440</v>
       </c>
       <c r="B2203">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2203">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D2203" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F2203" t="s">
-        <v>612</v>
+        <v>224</v>
       </c>
       <c r="G2203" t="s">
-        <v>613</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2204">
-        <v>8312409</v>
+        <v>8310645</v>
       </c>
       <c r="B2204">
-        <v>2645</v>
+        <v>1763</v>
       </c>
       <c r="C2204">
         <v>509</v>
       </c>
       <c r="D2204" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="F2204" t="s">
         <v>612</v>
@@ -46130,16 +46124,16 @@
     </row>
     <row r="2205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2205">
-        <v>8315055</v>
+        <v>8312409</v>
       </c>
       <c r="B2205">
-        <v>1322</v>
+        <v>2645</v>
       </c>
       <c r="C2205">
         <v>509</v>
       </c>
       <c r="D2205" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F2205" t="s">
         <v>612</v>
@@ -46150,16 +46144,16 @@
     </row>
     <row r="2206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2206">
-        <v>8316378</v>
+        <v>8315055</v>
       </c>
       <c r="B2206">
-        <v>2645</v>
+        <v>1322</v>
       </c>
       <c r="C2206">
         <v>509</v>
       </c>
       <c r="D2206" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F2206" t="s">
         <v>612</v>
@@ -46170,16 +46164,16 @@
     </row>
     <row r="2207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2207">
-        <v>8319024</v>
+        <v>8316378</v>
       </c>
       <c r="B2207">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2207">
         <v>509</v>
       </c>
       <c r="D2207" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2207" t="s">
         <v>612</v>
@@ -46190,16 +46184,16 @@
     </row>
     <row r="2208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2208">
-        <v>8321229</v>
+        <v>8319024</v>
       </c>
       <c r="B2208">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2208">
         <v>509</v>
       </c>
       <c r="D2208" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2208" t="s">
         <v>612</v>
@@ -46210,36 +46204,36 @@
     </row>
     <row r="2209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2209">
-        <v>8323875</v>
+        <v>8321229</v>
       </c>
       <c r="B2209">
-        <v>1322</v>
+        <v>2645</v>
       </c>
       <c r="C2209">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D2209" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F2209" t="s">
-        <v>465</v>
+        <v>612</v>
       </c>
       <c r="G2209" t="s">
-        <v>466</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2210">
-        <v>8325198</v>
+        <v>8323875</v>
       </c>
       <c r="B2210">
-        <v>3527</v>
+        <v>1322</v>
       </c>
       <c r="C2210">
         <v>510</v>
       </c>
       <c r="D2210" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F2210" t="s">
         <v>465</v>
@@ -46250,16 +46244,16 @@
     </row>
     <row r="2211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2211">
-        <v>8328726</v>
+        <v>8325198</v>
       </c>
       <c r="B2211">
-        <v>4409</v>
+        <v>3527</v>
       </c>
       <c r="C2211">
         <v>510</v>
       </c>
       <c r="D2211" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F2211" t="s">
         <v>465</v>
@@ -46270,16 +46264,16 @@
     </row>
     <row r="2212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2212">
-        <v>8333136</v>
+        <v>8328726</v>
       </c>
       <c r="B2212">
-        <v>2645</v>
+        <v>4409</v>
       </c>
       <c r="C2212">
         <v>510</v>
       </c>
       <c r="D2212" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F2212" t="s">
         <v>465</v>
@@ -46290,16 +46284,16 @@
     </row>
     <row r="2213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2213">
-        <v>8335782</v>
+        <v>8333136</v>
       </c>
       <c r="B2213">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2213">
         <v>510</v>
       </c>
       <c r="D2213" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F2213" t="s">
         <v>465</v>
@@ -46310,16 +46304,16 @@
     </row>
     <row r="2214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2214">
-        <v>8339310</v>
+        <v>8335782</v>
       </c>
       <c r="B2214">
-        <v>3086</v>
+        <v>3527</v>
       </c>
       <c r="C2214">
         <v>510</v>
       </c>
       <c r="D2214" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F2214" t="s">
         <v>465</v>
@@ -46329,11 +46323,17 @@
       </c>
     </row>
     <row r="2215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2215">
+        <v>8339310</v>
+      </c>
+      <c r="B2215">
+        <v>3086</v>
+      </c>
       <c r="C2215">
         <v>510</v>
       </c>
       <c r="D2215" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2215" t="s">
         <v>465</v>
@@ -46343,37 +46343,31 @@
       </c>
     </row>
     <row r="2216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2216">
-        <v>8342397</v>
-      </c>
-      <c r="B2216">
-        <v>4409</v>
-      </c>
       <c r="C2216">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D2216" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2216" t="s">
-        <v>90</v>
+        <v>465</v>
       </c>
       <c r="G2216" t="s">
-        <v>91</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2217">
-        <v>8346807</v>
+        <v>8342397</v>
       </c>
       <c r="B2217">
-        <v>2204</v>
+        <v>4409</v>
       </c>
       <c r="C2217">
         <v>511</v>
       </c>
       <c r="D2217" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2217" t="s">
         <v>90</v>
@@ -46384,27 +46378,27 @@
     </row>
     <row r="2218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2218">
-        <v>8349012</v>
+        <v>8346807</v>
       </c>
       <c r="B2218">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2218">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D2218" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2218" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="G2218" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2219">
-        <v>8351658</v>
+        <v>8349012</v>
       </c>
       <c r="B2219">
         <v>2645</v>
@@ -46413,7 +46407,7 @@
         <v>512</v>
       </c>
       <c r="D2219" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2219" t="s">
         <v>121</v>
@@ -46424,36 +46418,36 @@
     </row>
     <row r="2220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2220">
-        <v>8354304</v>
+        <v>8351658</v>
       </c>
       <c r="B2220">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2220">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D2220" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F2220" t="s">
-        <v>529</v>
+        <v>121</v>
       </c>
       <c r="G2220" t="s">
-        <v>530</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2221">
-        <v>8356068</v>
+        <v>8354304</v>
       </c>
       <c r="B2221">
-        <v>4409</v>
+        <v>1763</v>
       </c>
       <c r="C2221">
         <v>513</v>
       </c>
       <c r="D2221" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F2221" t="s">
         <v>529</v>
@@ -46464,16 +46458,16 @@
     </row>
     <row r="2222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2222">
-        <v>8360478</v>
+        <v>8356068</v>
       </c>
       <c r="B2222">
-        <v>1322</v>
+        <v>4409</v>
       </c>
       <c r="C2222">
         <v>513</v>
       </c>
       <c r="D2222" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F2222" t="s">
         <v>529</v>
@@ -46484,16 +46478,16 @@
     </row>
     <row r="2223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2223">
-        <v>8361801</v>
+        <v>8360478</v>
       </c>
       <c r="B2223">
-        <v>2204</v>
+        <v>1322</v>
       </c>
       <c r="C2223">
         <v>513</v>
       </c>
       <c r="D2223" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F2223" t="s">
         <v>529</v>
@@ -46504,36 +46498,36 @@
     </row>
     <row r="2224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2224">
-        <v>8364006</v>
+        <v>8361801</v>
       </c>
       <c r="B2224">
-        <v>3527</v>
+        <v>2204</v>
       </c>
       <c r="C2224">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D2224" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F2224" t="s">
-        <v>90</v>
+        <v>529</v>
       </c>
       <c r="G2224" t="s">
-        <v>91</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2225">
-        <v>8367534</v>
+        <v>8364006</v>
       </c>
       <c r="B2225">
-        <v>5291</v>
+        <v>3527</v>
       </c>
       <c r="C2225">
         <v>514</v>
       </c>
       <c r="D2225" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2225" t="s">
         <v>90</v>
@@ -46543,31 +46537,31 @@
       </c>
     </row>
     <row r="2226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2226">
+        <v>8367534</v>
+      </c>
+      <c r="B2226">
+        <v>5291</v>
+      </c>
       <c r="C2226">
         <v>514</v>
       </c>
       <c r="D2226" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F2226" t="s">
-        <v>614</v>
+        <v>90</v>
       </c>
       <c r="G2226" t="s">
-        <v>615</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2227" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2227">
-        <v>8372826</v>
-      </c>
-      <c r="B2227">
-        <v>5291</v>
-      </c>
       <c r="C2227">
         <v>515</v>
       </c>
       <c r="D2227" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F2227" t="s">
         <v>614</v>
@@ -46578,16 +46572,16 @@
     </row>
     <row r="2228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2228">
-        <v>8378118</v>
+        <v>8372826</v>
       </c>
       <c r="B2228">
-        <v>1322</v>
+        <v>5291</v>
       </c>
       <c r="C2228">
         <v>515</v>
       </c>
       <c r="D2228" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F2228" t="s">
         <v>614</v>
@@ -46598,16 +46592,16 @@
     </row>
     <row r="2229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2229">
-        <v>8379441</v>
+        <v>8378118</v>
       </c>
       <c r="B2229">
-        <v>4409</v>
+        <v>1322</v>
       </c>
       <c r="C2229">
         <v>515</v>
       </c>
       <c r="D2229" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F2229" t="s">
         <v>614</v>
@@ -46618,16 +46612,16 @@
     </row>
     <row r="2230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2230">
-        <v>8383851</v>
+        <v>8379441</v>
       </c>
       <c r="B2230">
-        <v>2645</v>
+        <v>4409</v>
       </c>
       <c r="C2230">
         <v>515</v>
       </c>
       <c r="D2230" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2230" t="s">
         <v>614</v>
@@ -46638,16 +46632,16 @@
     </row>
     <row r="2231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2231">
-        <v>8386497</v>
+        <v>8383851</v>
       </c>
       <c r="B2231">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2231">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D2231" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2231" t="s">
         <v>614</v>
@@ -46658,56 +46652,56 @@
     </row>
     <row r="2232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2232">
-        <v>8388261</v>
+        <v>8386497</v>
       </c>
       <c r="B2232">
         <v>1763</v>
       </c>
       <c r="C2232">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D2232" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F2232" t="s">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="G2232" t="s">
-        <v>51</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2233">
-        <v>8390025</v>
+        <v>8388261</v>
       </c>
       <c r="B2233">
-        <v>4409</v>
+        <v>1763</v>
       </c>
       <c r="C2233">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D2233" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F2233" t="s">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="G2233" t="s">
-        <v>617</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2234">
-        <v>8394435</v>
+        <v>8390025</v>
       </c>
       <c r="B2234">
-        <v>2645</v>
+        <v>4409</v>
       </c>
       <c r="C2234">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2234" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F2234" t="s">
         <v>616</v>
@@ -46718,16 +46712,16 @@
     </row>
     <row r="2235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2235">
-        <v>8397081</v>
+        <v>8394435</v>
       </c>
       <c r="B2235">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2235">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2235" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2235" t="s">
         <v>616</v>
@@ -46738,16 +46732,16 @@
     </row>
     <row r="2236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2236">
-        <v>8398845</v>
+        <v>8397081</v>
       </c>
       <c r="B2236">
-        <v>3086</v>
+        <v>1763</v>
       </c>
       <c r="C2236">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2236" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2236" t="s">
         <v>616</v>
@@ -46758,16 +46752,16 @@
     </row>
     <row r="2237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2237">
-        <v>8401932</v>
+        <v>8398845</v>
       </c>
       <c r="B2237">
-        <v>1763</v>
+        <v>3086</v>
       </c>
       <c r="C2237">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2237" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F2237" t="s">
         <v>616</v>
@@ -46778,16 +46772,16 @@
     </row>
     <row r="2238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2238">
-        <v>8403696</v>
+        <v>8401932</v>
       </c>
       <c r="B2238">
-        <v>6173</v>
+        <v>1763</v>
       </c>
       <c r="C2238">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2238" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F2238" t="s">
         <v>616</v>
@@ -46798,16 +46792,16 @@
     </row>
     <row r="2239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2239">
-        <v>8409870</v>
+        <v>8403696</v>
       </c>
       <c r="B2239">
-        <v>3968</v>
+        <v>6173</v>
       </c>
       <c r="C2239">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2239" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F2239" t="s">
         <v>616</v>
@@ -46818,16 +46812,16 @@
     </row>
     <row r="2240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2240">
-        <v>8413839</v>
+        <v>8409870</v>
       </c>
       <c r="B2240">
-        <v>7937</v>
+        <v>3968</v>
       </c>
       <c r="C2240">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2240" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F2240" t="s">
         <v>616</v>
@@ -46838,16 +46832,16 @@
     </row>
     <row r="2241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2241">
-        <v>8421777</v>
+        <v>8413839</v>
       </c>
       <c r="B2241">
-        <v>3086</v>
+        <v>7937</v>
       </c>
       <c r="C2241">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2241" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F2241" t="s">
         <v>616</v>
@@ -46858,16 +46852,16 @@
     </row>
     <row r="2242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2242">
-        <v>8424864</v>
+        <v>8421777</v>
       </c>
       <c r="B2242">
-        <v>6614</v>
+        <v>3086</v>
       </c>
       <c r="C2242">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D2242" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="F2242" t="s">
         <v>616</v>
@@ -46878,36 +46872,36 @@
     </row>
     <row r="2243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2243">
-        <v>8459262</v>
+        <v>8424864</v>
       </c>
       <c r="B2243">
-        <v>1322</v>
+        <v>6614</v>
       </c>
       <c r="C2243">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D2243" t="s">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="F2243" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G2243" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2244">
-        <v>8460585</v>
+        <v>8459262</v>
       </c>
       <c r="B2244">
-        <v>3527</v>
+        <v>1322</v>
       </c>
       <c r="C2244">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2244" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F2244" t="s">
         <v>618</v>
@@ -46918,16 +46912,16 @@
     </row>
     <row r="2245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2245">
-        <v>8464113</v>
+        <v>8460585</v>
       </c>
       <c r="B2245">
-        <v>5291</v>
+        <v>3527</v>
       </c>
       <c r="C2245">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2245" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F2245" t="s">
         <v>618</v>
@@ -46938,16 +46932,16 @@
     </row>
     <row r="2246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2246">
-        <v>8469405</v>
+        <v>8464113</v>
       </c>
       <c r="B2246">
-        <v>1763</v>
+        <v>5291</v>
       </c>
       <c r="C2246">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2246" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F2246" t="s">
         <v>618</v>
@@ -46958,16 +46952,16 @@
     </row>
     <row r="2247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2247">
-        <v>8471169</v>
+        <v>8469405</v>
       </c>
       <c r="B2247">
-        <v>5291</v>
+        <v>1763</v>
       </c>
       <c r="C2247">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2247" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F2247" t="s">
         <v>618</v>
@@ -46978,16 +46972,16 @@
     </row>
     <row r="2248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2248">
-        <v>8476461</v>
+        <v>8471169</v>
       </c>
       <c r="B2248">
-        <v>2645</v>
+        <v>5291</v>
       </c>
       <c r="C2248">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2248" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F2248" t="s">
         <v>618</v>
@@ -46998,16 +46992,16 @@
     </row>
     <row r="2249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2249">
-        <v>8479107</v>
+        <v>8476461</v>
       </c>
       <c r="B2249">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2249">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2249" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2249" t="s">
         <v>618</v>
@@ -47018,16 +47012,16 @@
     </row>
     <row r="2250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2250">
-        <v>8481312</v>
+        <v>8479107</v>
       </c>
       <c r="B2250">
         <v>2204</v>
       </c>
       <c r="C2250">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2250" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F2250" t="s">
         <v>618</v>
@@ -47038,16 +47032,16 @@
     </row>
     <row r="2251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2251">
-        <v>8483517</v>
+        <v>8481312</v>
       </c>
       <c r="B2251">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2251">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D2251" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F2251" t="s">
         <v>618</v>
@@ -47058,36 +47052,36 @@
     </row>
     <row r="2252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2252">
-        <v>8486163</v>
+        <v>8483517</v>
       </c>
       <c r="B2252">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2252">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D2252" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F2252" t="s">
-        <v>491</v>
+        <v>618</v>
       </c>
       <c r="G2252" t="s">
-        <v>338</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2253">
-        <v>8487927</v>
+        <v>8486163</v>
       </c>
       <c r="B2253">
-        <v>3968</v>
+        <v>1763</v>
       </c>
       <c r="C2253">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D2253" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="F2253" t="s">
         <v>491</v>
@@ -47098,16 +47092,16 @@
     </row>
     <row r="2254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2254">
-        <v>8491896</v>
+        <v>8487927</v>
       </c>
       <c r="B2254">
-        <v>6614</v>
+        <v>3968</v>
       </c>
       <c r="C2254">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D2254" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="F2254" t="s">
         <v>491</v>
@@ -47118,36 +47112,36 @@
     </row>
     <row r="2255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2255">
-        <v>8498511</v>
+        <v>8491896</v>
       </c>
       <c r="B2255">
-        <v>2645</v>
+        <v>6614</v>
       </c>
       <c r="C2255">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D2255" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2255" t="s">
-        <v>620</v>
+        <v>491</v>
       </c>
       <c r="G2255" t="s">
-        <v>621</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2256">
-        <v>8501157</v>
+        <v>8498511</v>
       </c>
       <c r="B2256">
-        <v>7055</v>
+        <v>2645</v>
       </c>
       <c r="C2256">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D2256" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F2256" t="s">
         <v>620</v>
@@ -47158,16 +47152,16 @@
     </row>
     <row r="2257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2257">
-        <v>8508213</v>
+        <v>8501157</v>
       </c>
       <c r="B2257">
-        <v>3086</v>
+        <v>7055</v>
       </c>
       <c r="C2257">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D2257" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2257" t="s">
         <v>620</v>
@@ -47178,16 +47172,16 @@
     </row>
     <row r="2258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2258">
-        <v>8511300</v>
+        <v>8508213</v>
       </c>
       <c r="B2258">
-        <v>4409</v>
+        <v>3086</v>
       </c>
       <c r="C2258">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D2258" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F2258" t="s">
         <v>620</v>
@@ -47198,16 +47192,16 @@
     </row>
     <row r="2259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2259">
-        <v>8515710</v>
+        <v>8511300</v>
       </c>
       <c r="B2259">
-        <v>3968</v>
+        <v>4409</v>
       </c>
       <c r="C2259">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D2259" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F2259" t="s">
         <v>620</v>
@@ -47218,16 +47212,16 @@
     </row>
     <row r="2260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2260">
-        <v>8519679</v>
+        <v>8515710</v>
       </c>
       <c r="B2260">
-        <v>1322</v>
+        <v>3968</v>
       </c>
       <c r="C2260">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D2260" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F2260" t="s">
         <v>620</v>
@@ -47238,36 +47232,36 @@
     </row>
     <row r="2261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2261">
-        <v>8521002</v>
+        <v>8519679</v>
       </c>
       <c r="B2261">
         <v>1322</v>
       </c>
       <c r="C2261">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D2261" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F2261" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G2261" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2262">
-        <v>8522325</v>
+        <v>8521002</v>
       </c>
       <c r="B2262">
-        <v>1763</v>
+        <v>1322</v>
       </c>
       <c r="C2262">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2262" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2262" t="s">
         <v>622</v>
@@ -47278,16 +47272,16 @@
     </row>
     <row r="2263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2263">
-        <v>8524089</v>
+        <v>8522325</v>
       </c>
       <c r="B2263">
-        <v>5291</v>
+        <v>1763</v>
       </c>
       <c r="C2263">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2263" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F2263" t="s">
         <v>622</v>
@@ -47298,16 +47292,16 @@
     </row>
     <row r="2264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2264">
-        <v>8529381</v>
+        <v>8524089</v>
       </c>
       <c r="B2264">
-        <v>1763</v>
+        <v>5291</v>
       </c>
       <c r="C2264">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2264" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F2264" t="s">
         <v>622</v>
@@ -47318,16 +47312,16 @@
     </row>
     <row r="2265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2265">
-        <v>8531145</v>
+        <v>8529381</v>
       </c>
       <c r="B2265">
-        <v>3086</v>
+        <v>1763</v>
       </c>
       <c r="C2265">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2265" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F2265" t="s">
         <v>622</v>
@@ -47338,16 +47332,16 @@
     </row>
     <row r="2266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2266">
-        <v>8534232</v>
+        <v>8531145</v>
       </c>
       <c r="B2266">
-        <v>1763</v>
+        <v>3086</v>
       </c>
       <c r="C2266">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2266" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F2266" t="s">
         <v>622</v>
@@ -47358,16 +47352,16 @@
     </row>
     <row r="2267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2267">
-        <v>8535996</v>
+        <v>8534232</v>
       </c>
       <c r="B2267">
-        <v>4850</v>
+        <v>1763</v>
       </c>
       <c r="C2267">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2267" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2267" t="s">
         <v>622</v>
@@ -47378,16 +47372,16 @@
     </row>
     <row r="2268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2268">
-        <v>8540847</v>
+        <v>8535996</v>
       </c>
       <c r="B2268">
-        <v>1322</v>
+        <v>4850</v>
       </c>
       <c r="C2268">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2268" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F2268" t="s">
         <v>622</v>
@@ -47398,16 +47392,16 @@
     </row>
     <row r="2269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2269">
-        <v>8542170</v>
+        <v>8540847</v>
       </c>
       <c r="B2269">
-        <v>4409</v>
+        <v>1322</v>
       </c>
       <c r="C2269">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2269" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2269" t="s">
         <v>622</v>
@@ -47418,36 +47412,36 @@
     </row>
     <row r="2270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2270">
-        <v>8546580</v>
+        <v>8542170</v>
       </c>
       <c r="B2270">
-        <v>3527</v>
+        <v>4409</v>
       </c>
       <c r="C2270">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D2270" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F2270" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G2270" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2271">
-        <v>8550108</v>
+        <v>8546580</v>
       </c>
       <c r="B2271">
-        <v>1763</v>
+        <v>3527</v>
       </c>
       <c r="C2271">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D2271" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F2271" t="s">
         <v>624</v>
@@ -47458,16 +47452,16 @@
     </row>
     <row r="2272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2272">
-        <v>8551872</v>
+        <v>8550108</v>
       </c>
       <c r="B2272">
-        <v>1322</v>
+        <v>1763</v>
       </c>
       <c r="C2272">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D2272" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="F2272" t="s">
         <v>624</v>
@@ -47478,16 +47472,16 @@
     </row>
     <row r="2273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2273">
-        <v>8553195</v>
+        <v>8551872</v>
       </c>
       <c r="B2273">
         <v>1322</v>
       </c>
       <c r="C2273">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D2273" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F2273" t="s">
         <v>624</v>
@@ -47498,16 +47492,16 @@
     </row>
     <row r="2274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2274">
-        <v>8554518</v>
+        <v>8553195</v>
       </c>
       <c r="B2274">
-        <v>5291</v>
+        <v>1322</v>
       </c>
       <c r="C2274">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D2274" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F2274" t="s">
         <v>624</v>
@@ -47518,36 +47512,36 @@
     </row>
     <row r="2275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2275">
-        <v>8559810</v>
+        <v>8554518</v>
       </c>
       <c r="B2275">
-        <v>1763</v>
+        <v>5291</v>
       </c>
       <c r="C2275">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D2275" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2275" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G2275" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="2276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2276">
-        <v>8561574</v>
+        <v>8559810</v>
       </c>
       <c r="B2276">
-        <v>3527</v>
+        <v>1763</v>
       </c>
       <c r="C2276">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2276" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2276" t="s">
         <v>626</v>
@@ -47558,16 +47552,16 @@
     </row>
     <row r="2277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2277">
-        <v>8565102</v>
+        <v>8561574</v>
       </c>
       <c r="B2277">
-        <v>3086</v>
+        <v>3527</v>
       </c>
       <c r="C2277">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2277" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2277" t="s">
         <v>626</v>
@@ -47578,16 +47572,16 @@
     </row>
     <row r="2278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2278">
-        <v>8568189</v>
+        <v>8565102</v>
       </c>
       <c r="B2278">
-        <v>5732</v>
+        <v>3086</v>
       </c>
       <c r="C2278">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2278" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F2278" t="s">
         <v>626</v>
@@ -47598,16 +47592,16 @@
     </row>
     <row r="2279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2279">
-        <v>8573922</v>
+        <v>8568189</v>
       </c>
       <c r="B2279">
-        <v>4850</v>
+        <v>5732</v>
       </c>
       <c r="C2279">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2279" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F2279" t="s">
         <v>626</v>
@@ -47618,16 +47612,16 @@
     </row>
     <row r="2280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2280">
-        <v>8578773</v>
+        <v>8573922</v>
       </c>
       <c r="B2280">
-        <v>1322</v>
+        <v>4850</v>
       </c>
       <c r="C2280">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2280" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F2280" t="s">
         <v>626</v>
@@ -47638,16 +47632,16 @@
     </row>
     <row r="2281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2281">
-        <v>8580096</v>
+        <v>8578773</v>
       </c>
       <c r="B2281">
-        <v>2645</v>
+        <v>1322</v>
       </c>
       <c r="C2281">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2281" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F2281" t="s">
         <v>626</v>
@@ -47658,36 +47652,36 @@
     </row>
     <row r="2282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2282">
-        <v>8582742</v>
+        <v>8580096</v>
       </c>
       <c r="B2282">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2282">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D2282" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2282" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G2282" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="2283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2283">
-        <v>8586270</v>
+        <v>8582742</v>
       </c>
       <c r="B2283">
-        <v>4850</v>
+        <v>3527</v>
       </c>
       <c r="C2283">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D2283" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2283" t="s">
         <v>628</v>
@@ -47698,16 +47692,16 @@
     </row>
     <row r="2284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2284">
-        <v>8591121</v>
+        <v>8586270</v>
       </c>
       <c r="B2284">
         <v>4850</v>
       </c>
       <c r="C2284">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D2284" t="s">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="F2284" t="s">
         <v>628</v>
@@ -47718,16 +47712,16 @@
     </row>
     <row r="2285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2285">
-        <v>8595972</v>
+        <v>8591121</v>
       </c>
       <c r="B2285">
-        <v>7496</v>
+        <v>4850</v>
       </c>
       <c r="C2285">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D2285" t="s">
-        <v>23</v>
+        <v>260</v>
       </c>
       <c r="F2285" t="s">
         <v>628</v>
@@ -47738,16 +47732,16 @@
     </row>
     <row r="2286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2286">
-        <v>8603469</v>
+        <v>8595972</v>
       </c>
       <c r="B2286">
-        <v>3968</v>
+        <v>7496</v>
       </c>
       <c r="C2286">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D2286" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2286" t="s">
         <v>628</v>
@@ -47758,16 +47752,16 @@
     </row>
     <row r="2287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2287">
-        <v>8607438</v>
+        <v>8603469</v>
       </c>
       <c r="B2287">
-        <v>7055</v>
+        <v>3968</v>
       </c>
       <c r="C2287">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D2287" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2287" t="s">
         <v>628</v>
@@ -47778,36 +47772,36 @@
     </row>
     <row r="2288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2288">
-        <v>8617140</v>
+        <v>8607438</v>
       </c>
       <c r="B2288">
-        <v>1322</v>
+        <v>7055</v>
       </c>
       <c r="C2288">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D2288" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="F2288" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G2288" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2289">
-        <v>8618463</v>
+        <v>8617140</v>
       </c>
       <c r="B2289">
-        <v>6173</v>
+        <v>1322</v>
       </c>
       <c r="C2289">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2289" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="F2289" t="s">
         <v>630</v>
@@ -47818,16 +47812,16 @@
     </row>
     <row r="2290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2290">
-        <v>8624637</v>
+        <v>8618463</v>
       </c>
       <c r="B2290">
-        <v>2645</v>
+        <v>6173</v>
       </c>
       <c r="C2290">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2290" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F2290" t="s">
         <v>630</v>
@@ -47838,16 +47832,16 @@
     </row>
     <row r="2291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2291">
-        <v>8627283</v>
+        <v>8624637</v>
       </c>
       <c r="B2291">
-        <v>8378</v>
+        <v>2645</v>
       </c>
       <c r="C2291">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2291" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F2291" t="s">
         <v>630</v>
@@ -47858,16 +47852,16 @@
     </row>
     <row r="2292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2292">
-        <v>8635662</v>
+        <v>8627283</v>
       </c>
       <c r="B2292">
-        <v>2645</v>
+        <v>8378</v>
       </c>
       <c r="C2292">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2292" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F2292" t="s">
         <v>630</v>
@@ -47878,16 +47872,16 @@
     </row>
     <row r="2293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2293">
-        <v>8638308</v>
+        <v>8635662</v>
       </c>
       <c r="B2293">
         <v>2645</v>
       </c>
       <c r="C2293">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2293" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2293" t="s">
         <v>630</v>
@@ -47898,16 +47892,16 @@
     </row>
     <row r="2294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2294">
-        <v>8640954</v>
+        <v>8638308</v>
       </c>
       <c r="B2294">
-        <v>1322</v>
+        <v>2645</v>
       </c>
       <c r="C2294">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2294" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F2294" t="s">
         <v>630</v>
@@ -47918,16 +47912,16 @@
     </row>
     <row r="2295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2295">
-        <v>8642277</v>
+        <v>8640954</v>
       </c>
       <c r="B2295">
-        <v>5732</v>
+        <v>1322</v>
       </c>
       <c r="C2295">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D2295" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F2295" t="s">
         <v>630</v>
@@ -47938,36 +47932,36 @@
     </row>
     <row r="2296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2296">
-        <v>8648010</v>
+        <v>8642277</v>
       </c>
       <c r="B2296">
-        <v>25577</v>
+        <v>5732</v>
       </c>
       <c r="C2296">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D2296" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F2296" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G2296" t="s">
-        <v>34</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2297">
-        <v>8673588</v>
+        <v>8648010</v>
       </c>
       <c r="B2297">
-        <v>2204</v>
+        <v>25577</v>
       </c>
       <c r="C2297">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D2297" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F2297" t="s">
         <v>632</v>
@@ -47978,36 +47972,36 @@
     </row>
     <row r="2298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2298">
-        <v>8675793</v>
+        <v>8673588</v>
       </c>
       <c r="B2298">
-        <v>1763</v>
+        <v>2204</v>
       </c>
       <c r="C2298">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D2298" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F2298" t="s">
-        <v>500</v>
+        <v>632</v>
       </c>
       <c r="G2298" t="s">
-        <v>501</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2299">
-        <v>8677557</v>
+        <v>8675793</v>
       </c>
       <c r="B2299">
         <v>1763</v>
       </c>
       <c r="C2299">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D2299" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F2299" t="s">
         <v>500</v>
@@ -48018,16 +48012,16 @@
     </row>
     <row r="2300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2300">
-        <v>8679321</v>
+        <v>8677557</v>
       </c>
       <c r="B2300">
-        <v>5291</v>
+        <v>1763</v>
       </c>
       <c r="C2300">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D2300" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F2300" t="s">
         <v>500</v>
@@ -48038,16 +48032,16 @@
     </row>
     <row r="2301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2301">
-        <v>8684613</v>
+        <v>8679321</v>
       </c>
       <c r="B2301">
-        <v>1322</v>
+        <v>5291</v>
       </c>
       <c r="C2301">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D2301" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F2301" t="s">
         <v>500</v>
@@ -48058,36 +48052,36 @@
     </row>
     <row r="2302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2302">
-        <v>8685936</v>
+        <v>8684613</v>
       </c>
       <c r="B2302">
-        <v>2645</v>
+        <v>1322</v>
       </c>
       <c r="C2302">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D2302" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F2302" t="s">
-        <v>609</v>
+        <v>500</v>
       </c>
       <c r="G2302" t="s">
-        <v>610</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2303">
-        <v>8688582</v>
+        <v>8685936</v>
       </c>
       <c r="B2303">
-        <v>3968</v>
+        <v>2645</v>
       </c>
       <c r="C2303">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D2303" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F2303" t="s">
         <v>609</v>
@@ -48098,16 +48092,16 @@
     </row>
     <row r="2304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2304">
-        <v>8692551</v>
+        <v>8688582</v>
       </c>
       <c r="B2304">
         <v>3968</v>
       </c>
       <c r="C2304">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D2304" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2304" t="s">
         <v>609</v>
@@ -48118,16 +48112,16 @@
     </row>
     <row r="2305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2305">
-        <v>8696520</v>
+        <v>8692551</v>
       </c>
       <c r="B2305">
-        <v>1322</v>
+        <v>3968</v>
       </c>
       <c r="C2305">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D2305" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2305" t="s">
         <v>609</v>
@@ -48138,16 +48132,16 @@
     </row>
     <row r="2306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2306">
-        <v>8697843</v>
+        <v>8696520</v>
       </c>
       <c r="B2306">
-        <v>3086</v>
+        <v>1322</v>
       </c>
       <c r="C2306">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D2306" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F2306" t="s">
         <v>609</v>
@@ -48158,36 +48152,36 @@
     </row>
     <row r="2307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2307">
-        <v>8700930</v>
+        <v>8697843</v>
       </c>
       <c r="B2307">
-        <v>1322</v>
+        <v>3086</v>
       </c>
       <c r="C2307">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D2307" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="F2307" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
       <c r="G2307" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2308">
-        <v>8702253</v>
+        <v>8700930</v>
       </c>
       <c r="B2308">
-        <v>8378</v>
+        <v>1322</v>
       </c>
       <c r="C2308">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D2308" t="s">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="F2308" t="s">
         <v>633</v>
@@ -48198,16 +48192,16 @@
     </row>
     <row r="2309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2309">
-        <v>8710632</v>
+        <v>8702253</v>
       </c>
       <c r="B2309">
-        <v>3527</v>
+        <v>8378</v>
       </c>
       <c r="C2309">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D2309" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F2309" t="s">
         <v>633</v>
@@ -48218,16 +48212,16 @@
     </row>
     <row r="2310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2310">
-        <v>8714160</v>
+        <v>8710632</v>
       </c>
       <c r="B2310">
         <v>3527</v>
       </c>
       <c r="C2310">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D2310" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F2310" t="s">
         <v>633</v>
@@ -48238,56 +48232,56 @@
     </row>
     <row r="2311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2311">
-        <v>8735328</v>
+        <v>8714160</v>
       </c>
       <c r="B2311">
-        <v>6173</v>
+        <v>3527</v>
       </c>
       <c r="C2311">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D2311" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F2311" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G2311" t="s">
-        <v>14</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2312">
-        <v>8753409</v>
+        <v>8735328</v>
       </c>
       <c r="B2312">
-        <v>3968</v>
+        <v>6173</v>
       </c>
       <c r="C2312">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D2312" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2312" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G2312" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2313">
-        <v>8757378</v>
+        <v>8753409</v>
       </c>
       <c r="B2313">
-        <v>2204</v>
+        <v>3968</v>
       </c>
       <c r="C2313">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D2313" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F2313" t="s">
         <v>636</v>
@@ -48298,16 +48292,16 @@
     </row>
     <row r="2314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2314">
-        <v>8759583</v>
+        <v>8757378</v>
       </c>
       <c r="B2314">
-        <v>3086</v>
+        <v>2204</v>
       </c>
       <c r="C2314">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D2314" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F2314" t="s">
         <v>636</v>
@@ -48318,36 +48312,36 @@
     </row>
     <row r="2315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2315">
-        <v>8762670</v>
+        <v>8759583</v>
       </c>
       <c r="B2315">
-        <v>1322</v>
+        <v>3086</v>
       </c>
       <c r="C2315">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D2315" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2315" t="s">
-        <v>33</v>
+        <v>636</v>
       </c>
       <c r="G2315" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2316">
-        <v>8763993</v>
+        <v>8762670</v>
       </c>
       <c r="B2316">
-        <v>1763</v>
+        <v>1322</v>
       </c>
       <c r="C2316">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D2316" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F2316" t="s">
         <v>33</v>
@@ -48358,56 +48352,56 @@
     </row>
     <row r="2317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2317">
-        <v>8765757</v>
+        <v>8763993</v>
       </c>
       <c r="B2317">
-        <v>2645</v>
+        <v>1763</v>
       </c>
       <c r="C2317">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D2317" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2317" t="s">
-        <v>328</v>
+        <v>33</v>
       </c>
       <c r="G2317" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2318">
-        <v>8768403</v>
+        <v>8765757</v>
       </c>
       <c r="B2318">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2318">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D2318" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F2318" t="s">
-        <v>94</v>
+        <v>328</v>
       </c>
       <c r="G2318" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2319">
-        <v>8770167</v>
+        <v>8768403</v>
       </c>
       <c r="B2319">
-        <v>6614</v>
+        <v>1763</v>
       </c>
       <c r="C2319">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D2319" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F2319" t="s">
         <v>94</v>
@@ -48418,16 +48412,16 @@
     </row>
     <row r="2320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2320">
-        <v>8776782</v>
+        <v>8770167</v>
       </c>
       <c r="B2320">
-        <v>2204</v>
+        <v>6614</v>
       </c>
       <c r="C2320">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D2320" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="F2320" t="s">
         <v>94</v>
@@ -48438,16 +48432,16 @@
     </row>
     <row r="2321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2321">
-        <v>8778987</v>
+        <v>8776782</v>
       </c>
       <c r="B2321">
-        <v>3527</v>
+        <v>2204</v>
       </c>
       <c r="C2321">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D2321" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F2321" t="s">
         <v>94</v>
@@ -48458,70 +48452,70 @@
     </row>
     <row r="2322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2322">
+        <v>8778987</v>
+      </c>
+      <c r="B2322">
+        <v>3527</v>
+      </c>
+      <c r="C2322">
+        <v>534</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2322" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2322" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2323">
         <v>8782515</v>
       </c>
-      <c r="B2322">
+      <c r="B2323">
         <v>3968</v>
       </c>
-      <c r="C2322">
-        <v>536</v>
-      </c>
-      <c r="D2322" t="s">
+      <c r="C2323">
+        <v>535</v>
+      </c>
+      <c r="D2323" t="s">
         <v>19</v>
-      </c>
-      <c r="F2322" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2322" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2323" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C2323">
-        <v>536</v>
-      </c>
-      <c r="D2323" t="s">
-        <v>23</v>
       </c>
       <c r="F2323" t="s">
         <v>90</v>
       </c>
       <c r="G2323" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C2324">
+        <v>535</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2324" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2324" t="s">
         <v>653</v>
-      </c>
-    </row>
-    <row r="2324" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2324">
-        <v>8786484</v>
-      </c>
-      <c r="B2324">
-        <v>2204</v>
-      </c>
-      <c r="C2324">
-        <v>537</v>
-      </c>
-      <c r="D2324" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2324" t="s">
-        <v>491</v>
-      </c>
-      <c r="G2324" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="2325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2325">
-        <v>8788689</v>
+        <v>8786484</v>
       </c>
       <c r="B2325">
-        <v>3527</v>
+        <v>2204</v>
       </c>
       <c r="C2325">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D2325" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="F2325" t="s">
         <v>491</v>
@@ -48532,16 +48526,16 @@
     </row>
     <row r="2326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2326">
-        <v>8792217</v>
+        <v>8788689</v>
       </c>
       <c r="B2326">
         <v>3527</v>
       </c>
       <c r="C2326">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D2326" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="F2326" t="s">
         <v>491</v>
@@ -48552,36 +48546,36 @@
     </row>
     <row r="2327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2327">
-        <v>8795745</v>
+        <v>8792217</v>
       </c>
       <c r="B2327">
-        <v>1322</v>
+        <v>3527</v>
       </c>
       <c r="C2327">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D2327" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="F2327" t="s">
-        <v>637</v>
+        <v>491</v>
       </c>
       <c r="G2327" t="s">
-        <v>638</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2328">
-        <v>8797068</v>
+        <v>8795745</v>
       </c>
       <c r="B2328">
-        <v>6173</v>
+        <v>1322</v>
       </c>
       <c r="C2328">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D2328" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="F2328" t="s">
         <v>637</v>
@@ -48592,16 +48586,16 @@
     </row>
     <row r="2329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2329">
-        <v>8803242</v>
+        <v>8797068</v>
       </c>
       <c r="B2329">
-        <v>2645</v>
+        <v>6173</v>
       </c>
       <c r="C2329">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D2329" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="F2329" t="s">
         <v>637</v>
@@ -48612,16 +48606,16 @@
     </row>
     <row r="2330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2330">
-        <v>8805888</v>
+        <v>8803242</v>
       </c>
       <c r="B2330">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2330">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D2330" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F2330" t="s">
         <v>637</v>
@@ -48632,16 +48626,16 @@
     </row>
     <row r="2331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2331">
-        <v>8809416</v>
+        <v>8805888</v>
       </c>
       <c r="B2331">
-        <v>1322</v>
+        <v>3527</v>
       </c>
       <c r="C2331">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D2331" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F2331" t="s">
         <v>637</v>
@@ -48652,16 +48646,16 @@
     </row>
     <row r="2332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2332">
-        <v>8810739</v>
+        <v>8809416</v>
       </c>
       <c r="B2332">
-        <v>2645</v>
+        <v>1322</v>
       </c>
       <c r="C2332">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D2332" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F2332" t="s">
         <v>637</v>
@@ -48672,36 +48666,36 @@
     </row>
     <row r="2333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2333">
-        <v>8813385</v>
+        <v>8810739</v>
       </c>
       <c r="B2333">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2333">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D2333" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F2333" t="s">
-        <v>315</v>
+        <v>637</v>
       </c>
       <c r="G2333" t="s">
-        <v>316</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2334">
-        <v>8815590</v>
+        <v>8813385</v>
       </c>
       <c r="B2334">
-        <v>4409</v>
+        <v>2204</v>
       </c>
       <c r="C2334">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D2334" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F2334" t="s">
         <v>315</v>
@@ -48712,16 +48706,16 @@
     </row>
     <row r="2335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2335">
-        <v>8820000</v>
+        <v>8815590</v>
       </c>
       <c r="B2335">
-        <v>1322</v>
+        <v>4409</v>
       </c>
       <c r="C2335">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D2335" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2335" t="s">
         <v>315</v>
@@ -48732,36 +48726,36 @@
     </row>
     <row r="2336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2336">
-        <v>8821323</v>
+        <v>8820000</v>
       </c>
       <c r="B2336">
-        <v>6614</v>
+        <v>1322</v>
       </c>
       <c r="C2336">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D2336" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2336" t="s">
-        <v>639</v>
+        <v>315</v>
       </c>
       <c r="G2336" t="s">
-        <v>640</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2337">
-        <v>8827938</v>
+        <v>8821323</v>
       </c>
       <c r="B2337">
-        <v>1322</v>
+        <v>6614</v>
       </c>
       <c r="C2337">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D2337" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="F2337" t="s">
         <v>639</v>
@@ -48772,16 +48766,16 @@
     </row>
     <row r="2338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2338">
-        <v>8829261</v>
+        <v>8827938</v>
       </c>
       <c r="B2338">
-        <v>5291</v>
+        <v>1322</v>
       </c>
       <c r="C2338">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D2338" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="F2338" t="s">
         <v>639</v>
@@ -48792,16 +48786,16 @@
     </row>
     <row r="2339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2339">
-        <v>8834553</v>
+        <v>8829261</v>
       </c>
       <c r="B2339">
-        <v>3527</v>
+        <v>5291</v>
       </c>
       <c r="C2339">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D2339" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F2339" t="s">
         <v>639</v>
@@ -48812,16 +48806,16 @@
     </row>
     <row r="2340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2340">
-        <v>8838081</v>
+        <v>8834553</v>
       </c>
       <c r="B2340">
-        <v>7055</v>
+        <v>3527</v>
       </c>
       <c r="C2340">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D2340" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2340" t="s">
         <v>639</v>
@@ -48832,56 +48826,56 @@
     </row>
     <row r="2341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2341">
-        <v>8845137</v>
+        <v>8838081</v>
       </c>
       <c r="B2341">
-        <v>2645</v>
+        <v>7055</v>
       </c>
       <c r="C2341">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D2341" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F2341" t="s">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="G2341" t="s">
-        <v>51</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2342">
-        <v>8847783</v>
+        <v>8845137</v>
       </c>
       <c r="B2342">
-        <v>3086</v>
+        <v>2645</v>
       </c>
       <c r="C2342">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D2342" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2342" t="s">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="G2342" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2343">
-        <v>8850870</v>
+        <v>8847783</v>
       </c>
       <c r="B2343">
-        <v>2204</v>
+        <v>3086</v>
       </c>
       <c r="C2343">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D2343" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F2343" t="s">
         <v>218</v>
@@ -48892,16 +48886,16 @@
     </row>
     <row r="2344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2344">
-        <v>8853075</v>
+        <v>8850870</v>
       </c>
       <c r="B2344">
-        <v>4409</v>
+        <v>2204</v>
       </c>
       <c r="C2344">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D2344" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F2344" t="s">
         <v>218</v>
@@ -48912,36 +48906,36 @@
     </row>
     <row r="2345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2345">
-        <v>8857485</v>
+        <v>8853075</v>
       </c>
       <c r="B2345">
-        <v>3527</v>
+        <v>4409</v>
       </c>
       <c r="C2345">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D2345" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F2345" t="s">
-        <v>641</v>
+        <v>218</v>
       </c>
       <c r="G2345" t="s">
-        <v>642</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2346">
-        <v>8861013</v>
+        <v>8857485</v>
       </c>
       <c r="B2346">
-        <v>5732</v>
+        <v>3527</v>
       </c>
       <c r="C2346">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D2346" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F2346" t="s">
         <v>641</v>
@@ -48952,16 +48946,16 @@
     </row>
     <row r="2347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2347">
-        <v>8866746</v>
+        <v>8861013</v>
       </c>
       <c r="B2347">
-        <v>2645</v>
+        <v>5732</v>
       </c>
       <c r="C2347">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D2347" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="F2347" t="s">
         <v>641</v>
@@ -48972,16 +48966,16 @@
     </row>
     <row r="2348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2348">
-        <v>8869392</v>
+        <v>8866746</v>
       </c>
       <c r="B2348">
         <v>2645</v>
       </c>
       <c r="C2348">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D2348" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F2348" t="s">
         <v>641</v>
@@ -48992,36 +48986,36 @@
     </row>
     <row r="2349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2349">
-        <v>8872038</v>
+        <v>8869392</v>
       </c>
       <c r="B2349">
         <v>2645</v>
       </c>
       <c r="C2349">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D2349" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F2349" t="s">
-        <v>90</v>
+        <v>641</v>
       </c>
       <c r="G2349" t="s">
-        <v>91</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2350">
-        <v>8874684</v>
+        <v>8872038</v>
       </c>
       <c r="B2350">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2350">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D2350" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2350" t="s">
         <v>90</v>
@@ -49032,36 +49026,36 @@
     </row>
     <row r="2351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2351">
-        <v>8876889</v>
+        <v>8874684</v>
       </c>
       <c r="B2351">
-        <v>3086</v>
+        <v>2204</v>
       </c>
       <c r="C2351">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D2351" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F2351" t="s">
-        <v>322</v>
+        <v>90</v>
       </c>
       <c r="G2351" t="s">
-        <v>323</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2352">
-        <v>8879976</v>
+        <v>8876889</v>
       </c>
       <c r="B2352">
-        <v>2204</v>
+        <v>3086</v>
       </c>
       <c r="C2352">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D2352" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F2352" t="s">
         <v>322</v>
@@ -49072,36 +49066,36 @@
     </row>
     <row r="2353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2353">
-        <v>8882181</v>
+        <v>8879976</v>
       </c>
       <c r="B2353">
-        <v>4850</v>
+        <v>2204</v>
       </c>
       <c r="C2353">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D2353" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F2353" t="s">
-        <v>643</v>
+        <v>322</v>
       </c>
       <c r="G2353" t="s">
-        <v>644</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2354">
-        <v>8887032</v>
+        <v>8882181</v>
       </c>
       <c r="B2354">
-        <v>2204</v>
+        <v>4850</v>
       </c>
       <c r="C2354">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D2354" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F2354" t="s">
         <v>643</v>
@@ -49111,11 +49105,17 @@
       </c>
     </row>
     <row r="2355" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2355">
+        <v>8887032</v>
+      </c>
+      <c r="B2355">
+        <v>2204</v>
+      </c>
       <c r="C2355">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D2355" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2355" t="s">
         <v>643</v>
@@ -49125,17 +49125,11 @@
       </c>
     </row>
     <row r="2356" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2356">
-        <v>8889237</v>
-      </c>
-      <c r="B2356">
-        <v>10142</v>
-      </c>
       <c r="C2356">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D2356" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2356" t="s">
         <v>643</v>
@@ -49146,16 +49140,16 @@
     </row>
     <row r="2357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2357">
-        <v>8899380</v>
+        <v>8889237</v>
       </c>
       <c r="B2357">
-        <v>2204</v>
+        <v>10142</v>
       </c>
       <c r="C2357">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D2357" t="s">
-        <v>270</v>
+        <v>14</v>
       </c>
       <c r="F2357" t="s">
         <v>643</v>
@@ -49166,16 +49160,16 @@
     </row>
     <row r="2358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2358">
-        <v>8901585</v>
+        <v>8899380</v>
       </c>
       <c r="B2358">
-        <v>4850</v>
+        <v>2204</v>
       </c>
       <c r="C2358">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D2358" t="s">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="F2358" t="s">
         <v>643</v>
@@ -49185,31 +49179,31 @@
       </c>
     </row>
     <row r="2359" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2359">
+        <v>8901585</v>
+      </c>
+      <c r="B2359">
+        <v>4850</v>
+      </c>
       <c r="C2359">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D2359" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2359" t="s">
+        <v>643</v>
+      </c>
+      <c r="G2359" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C2360">
+        <v>546</v>
+      </c>
+      <c r="D2360" t="s">
         <v>50</v>
-      </c>
-      <c r="F2359" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2359" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2360" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2360">
-        <v>8906436</v>
-      </c>
-      <c r="B2360">
-        <v>2645</v>
-      </c>
-      <c r="C2360">
-        <v>547</v>
-      </c>
-      <c r="D2360" t="s">
-        <v>30</v>
       </c>
       <c r="F2360" t="s">
         <v>105</v>
@@ -49220,36 +49214,36 @@
     </row>
     <row r="2361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2361">
-        <v>8909082</v>
+        <v>8906436</v>
       </c>
       <c r="B2361">
-        <v>3527</v>
+        <v>2645</v>
       </c>
       <c r="C2361">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D2361" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F2361" t="s">
-        <v>645</v>
+        <v>105</v>
       </c>
       <c r="G2361" t="s">
-        <v>646</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2362">
-        <v>8912610</v>
+        <v>8909082</v>
       </c>
       <c r="B2362">
-        <v>2645</v>
+        <v>3527</v>
       </c>
       <c r="C2362">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D2362" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F2362" t="s">
         <v>645</v>
@@ -49260,16 +49254,16 @@
     </row>
     <row r="2363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2363">
-        <v>8915256</v>
+        <v>8912610</v>
       </c>
       <c r="B2363">
-        <v>6173</v>
+        <v>2645</v>
       </c>
       <c r="C2363">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D2363" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F2363" t="s">
         <v>645</v>
@@ -49280,16 +49274,16 @@
     </row>
     <row r="2364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2364">
-        <v>8921430</v>
+        <v>8915256</v>
       </c>
       <c r="B2364">
-        <v>2645</v>
+        <v>6173</v>
       </c>
       <c r="C2364">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D2364" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F2364" t="s">
         <v>645</v>
@@ -49300,16 +49294,16 @@
     </row>
     <row r="2365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2365">
-        <v>8924076</v>
+        <v>8921430</v>
       </c>
       <c r="B2365">
-        <v>1763</v>
+        <v>2645</v>
       </c>
       <c r="C2365">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D2365" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2365" t="s">
         <v>645</v>
@@ -49320,16 +49314,16 @@
     </row>
     <row r="2366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2366">
-        <v>8925840</v>
+        <v>8924076</v>
       </c>
       <c r="B2366">
-        <v>2204</v>
+        <v>1763</v>
       </c>
       <c r="C2366">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D2366" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F2366" t="s">
         <v>645</v>
@@ -49340,36 +49334,36 @@
     </row>
     <row r="2367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2367">
-        <v>8928045</v>
+        <v>8925840</v>
       </c>
       <c r="B2367">
-        <v>2645</v>
+        <v>2204</v>
       </c>
       <c r="C2367">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D2367" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2367" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G2367" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="2368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2368">
-        <v>8930691</v>
+        <v>8928045</v>
       </c>
       <c r="B2368">
-        <v>2204</v>
+        <v>2645</v>
       </c>
       <c r="C2368">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D2368" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2368" t="s">
         <v>647</v>
@@ -49378,18 +49372,18 @@
         <v>648</v>
       </c>
     </row>
-    <row r="2369" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2369">
-        <v>8932896</v>
+        <v>8930691</v>
       </c>
       <c r="B2369">
-        <v>3527</v>
+        <v>2204</v>
       </c>
       <c r="C2369">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D2369" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F2369" t="s">
         <v>647</v>
@@ -49398,18 +49392,18 @@
         <v>648</v>
       </c>
     </row>
-    <row r="2370" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2370">
-        <v>8936424</v>
+        <v>8932896</v>
       </c>
       <c r="B2370">
-        <v>4409</v>
+        <v>3527</v>
       </c>
       <c r="C2370">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D2370" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F2370" t="s">
         <v>647</v>
@@ -49418,18 +49412,18 @@
         <v>648</v>
       </c>
     </row>
-    <row r="2371" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2371">
-        <v>8940834</v>
+        <v>8936424</v>
       </c>
       <c r="B2371">
-        <v>6614</v>
+        <v>4409</v>
       </c>
       <c r="C2371">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D2371" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F2371" t="s">
         <v>647</v>
@@ -49438,18 +49432,18 @@
         <v>648</v>
       </c>
     </row>
-    <row r="2372" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2372">
-        <v>8947449</v>
+        <v>8940834</v>
       </c>
       <c r="B2372">
-        <v>4409</v>
+        <v>6614</v>
       </c>
       <c r="C2372">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D2372" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2372" t="s">
         <v>647</v>
@@ -49458,18 +49452,18 @@
         <v>648</v>
       </c>
     </row>
-    <row r="2373" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2373">
-        <v>8951859</v>
+        <v>8947449</v>
       </c>
       <c r="B2373">
-        <v>2645</v>
+        <v>4409</v>
       </c>
       <c r="C2373">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D2373" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F2373" t="s">
         <v>647</v>
@@ -49478,38 +49472,38 @@
         <v>648</v>
       </c>
     </row>
-    <row r="2374" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2374">
+        <v>8951859</v>
+      </c>
+      <c r="B2374">
+        <v>2645</v>
+      </c>
+      <c r="C2374">
+        <v>548</v>
+      </c>
+      <c r="D2374" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2374" t="s">
+        <v>647</v>
+      </c>
+      <c r="G2374" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2375">
         <v>8954505</v>
       </c>
-      <c r="B2374">
+      <c r="B2375">
         <v>18080</v>
       </c>
-      <c r="C2374">
-        <v>550</v>
-      </c>
-      <c r="D2374" t="s">
+      <c r="C2375">
+        <v>549</v>
+      </c>
+      <c r="D2375" t="s">
         <v>32</v>
-      </c>
-      <c r="F2374" t="s">
-        <v>649</v>
-      </c>
-      <c r="G2374" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="2375" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2375">
-        <v>8972586</v>
-      </c>
-      <c r="B2375">
-        <v>7055</v>
-      </c>
-      <c r="C2375">
-        <v>550</v>
-      </c>
-      <c r="D2375" t="s">
-        <v>50</v>
       </c>
       <c r="F2375" t="s">
         <v>649</v>
@@ -49518,18 +49512,18 @@
         <v>650</v>
       </c>
     </row>
-    <row r="2376" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2376">
-        <v>8979642</v>
+        <v>8972586</v>
       </c>
       <c r="B2376">
-        <v>5291</v>
+        <v>7055</v>
       </c>
       <c r="C2376">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D2376" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F2376" t="s">
         <v>649</v>
@@ -49538,38 +49532,38 @@
         <v>650</v>
       </c>
     </row>
-    <row r="2377" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2377">
+        <v>8979642</v>
+      </c>
+      <c r="B2377">
+        <v>5291</v>
+      </c>
+      <c r="C2377">
+        <v>549</v>
+      </c>
+      <c r="D2377" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2377" t="s">
+        <v>649</v>
+      </c>
+      <c r="G2377" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2378">
         <v>8991990</v>
       </c>
-      <c r="B2377">
+      <c r="B2378">
         <v>3527</v>
       </c>
-      <c r="C2377">
-        <v>551</v>
-      </c>
-      <c r="D2377" t="s">
+      <c r="C2378">
+        <v>550</v>
+      </c>
+      <c r="D2378" t="s">
         <v>27</v>
-      </c>
-      <c r="F2377" t="s">
-        <v>651</v>
-      </c>
-      <c r="G2377" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="2378" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2378">
-        <v>8995518</v>
-      </c>
-      <c r="B2378">
-        <v>1322</v>
-      </c>
-      <c r="C2378">
-        <v>551</v>
-      </c>
-      <c r="D2378" t="s">
-        <v>21</v>
       </c>
       <c r="F2378" t="s">
         <v>651</v>
@@ -49578,18 +49572,18 @@
         <v>652</v>
       </c>
     </row>
-    <row r="2379" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2379">
-        <v>8996841</v>
+        <v>8995518</v>
       </c>
       <c r="B2379">
         <v>1322</v>
       </c>
       <c r="C2379">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D2379" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2379" t="s">
         <v>651</v>
@@ -49598,18 +49592,18 @@
         <v>652</v>
       </c>
     </row>
-    <row r="2380" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2380">
-        <v>8998164</v>
+        <v>8996841</v>
       </c>
       <c r="B2380">
-        <v>7496</v>
+        <v>1322</v>
       </c>
       <c r="C2380">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D2380" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2380" t="s">
         <v>651</v>
@@ -49618,18 +49612,18 @@
         <v>652</v>
       </c>
     </row>
-    <row r="2381" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2381">
-        <v>9005661</v>
+        <v>8998164</v>
       </c>
       <c r="B2381">
-        <v>5291</v>
+        <v>7496</v>
       </c>
       <c r="C2381">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D2381" t="s">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="F2381" t="s">
         <v>651</v>
@@ -49638,18 +49632,18 @@
         <v>652</v>
       </c>
     </row>
-    <row r="2382" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2382">
-        <v>9010953</v>
+        <v>9005661</v>
       </c>
       <c r="B2382">
-        <v>3527</v>
+        <v>5291</v>
       </c>
       <c r="C2382">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D2382" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="F2382" t="s">
         <v>651</v>
@@ -49658,10 +49652,30 @@
         <v>652</v>
       </c>
     </row>
-    <row r="2384" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2384" s="3"/>
-      <c r="H2384" t="str" cm="1">
-        <f t="array" ref="H2384">IF(G2384&lt;&gt;G2383,_xlfn.TEXTSPLIT(G2384," "),"")</f>
+    <row r="2383" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2383">
+        <v>9010953</v>
+      </c>
+      <c r="B2383">
+        <v>3527</v>
+      </c>
+      <c r="C2383">
+        <v>550</v>
+      </c>
+      <c r="D2383" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2383" t="s">
+        <v>651</v>
+      </c>
+      <c r="G2383" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2385" s="3"/>
+      <c r="H2385" t="str" cm="1">
+        <f t="array" ref="H2385">IF(G2385&lt;&gt;G2384,_xlfn.TEXTSPLIT(G2385," "),"")</f>
         <v/>
       </c>
     </row>

--- a/data/phoneme_onset_D/St10_D.xlsx
+++ b/data/phoneme_onset_D/St10_D.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/IMT/TESI/linguistic_pipeline_EEG/data/phoneme_onset_D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="6_{D6F9A13C-254F-4EFF-BB37-6ACBF87AA487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB392BCC-5E29-4746-BC9E-28BDDC153C07}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="6_{D6F9A13C-254F-4EFF-BB37-6ACBF87AA487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83AF5B51-8D9B-412B-8FBF-1BB5CCEFF329}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$2385</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -16873,6 +16876,9 @@
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C729">
+        <v>174</v>
+      </c>
       <c r="D729" t="s">
         <v>23</v>
       </c>
@@ -18426,6 +18432,9 @@
       </c>
     </row>
     <row r="808" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C808">
+        <v>191</v>
+      </c>
       <c r="D808" t="s">
         <v>23</v>
       </c>
@@ -49680,6 +49689,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C2385" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
